--- a/WizAccountant.xlsx
+++ b/WizAccountant.xlsx
@@ -8,15 +8,17 @@
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Phase Summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Features" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Success Criteria" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Platform (Cross-Phase)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Mobile Strategy" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Sage Module Priority" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Not Building (Plan 1)" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Phase 1 Exclusions" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="SDK Limits (Phase 3+)" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Phase 1 Checklist" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Phase Summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Features" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Success Criteria" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Platform (Cross-Phase)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Mobile Strategy" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Sage Module Priority" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Not Building (Plan 1)" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Phase 1 Exclusions" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="SDK Limits (Phase 3+)" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Execution Status" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -40,7 +42,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -50,6 +52,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -85,7 +102,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -94,6 +111,9 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -617,6 +637,86 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:A9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="36" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Excluded from Phase 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>AI chat</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Workflows</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Writes to ledger</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Multi-site analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Native mobile app (API only in P1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Inventory documents</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Orders Process()</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Allocations</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -677,7 +777,1596 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Work item</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Updated (UTC)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>P1-01: Create WizAccountant.slnx + Contracts, Api, Connector projects</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>P1-02: Shared DTOs: pairing, site, job, heartbeat, run-job message</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Contracts</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>P1-03: SQLite persistence (sites, pairing codes, jobs)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>P1-04: POST /api/pairing-codes — generate pairing code</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>P1-05: POST /api/sites/pair — register connector site</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>P1-06: GET /api/sites — list sites + online status</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>P1-07: POST/GET /api/jobs — submit job, poll result</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>P1-08: SignalR Connector Hub — register, heartbeat, route RunJob</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>P1-09: Worker service: pair on first run, save site state</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>P1-10: Connect to hub, register site, 30s heartbeat loop</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>P1-11: Receive RunJob, execute handler, POST job result</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>P1-12: Job shell: Site.Health (mock)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>P1-13: Job shell: Customer.List (mock)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>P1-14: dotnet build WizAccountant.slnx succeeds</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>P1-15: Wire Pastel.Evolution SDK — Site.Health (live DB)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>P1-16: SDK handler: GLAccount.List + GLAccount.Get</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>P1-17: SDK handler: Customer.List + Customer.Get</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Next</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>P1-18: SDK handler: CustomerTransaction.List (criteria)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>P1-19: SDK handler: Supplier.List + SupplierTransaction.List</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>P1-20: Evolution connection profile + Agent.Authenticate (appsettings; DPAPI next)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>P1-21: WizConnector.Tray — pairing wizard, status, device ID</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>P1-22: Auth stub — tenants + users (minimal)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>P1-23: Admin UI — create pairing code, list sites, Test connection</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>P1-24: Job wait/poll helper — sync read with timeout (30–60s)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>P1-25: Basic audit log table for all jobs</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>P1-26: REST long-poll fallback when WebSocket down</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>P1-27: Evolution version matrix + pilot install guide</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>P1-28: End-to-end test on pilot site #1 (pair → online → Customer.List)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Pilot</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>P1-29: End-to-end test on pilot site #2 (second Evolution version)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Pilot</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>P1-30: Site Online within 60s of connector start</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="72" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>P1-01</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Create WizAccountant.slnx + Contracts, Api, Connector projects</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>P1-02</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Contracts</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Shared DTOs: pairing, site, job, heartbeat, run-job message</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>P1-03</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>SQLite persistence (sites, pairing codes, jobs)</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>P1-04</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/pairing-codes — generate pairing code</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>P1-05</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/sites/pair — register connector site</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>P1-06</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>GET /api/sites — list sites + online status</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>P1-07</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>POST/GET /api/jobs — submit job, poll result</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>P1-08</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>SignalR Connector Hub — register, heartbeat, route RunJob</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>P1-09</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Worker service: pair on first run, save site state</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>P1-10</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Connect to hub, register site, 30s heartbeat loop</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>P1-11</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Receive RunJob, execute handler, POST job result</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>P1-12</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Job shell: Site.Health (mock)</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>P1-13</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Job shell: Customer.List (mock)</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>P1-14</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>dotnet build WizAccountant.slnx succeeds</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>P1-15</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Wire Pastel.Evolution SDK — Site.Health (live DB)</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>P1-16</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>SDK handler: GLAccount.List + GLAccount.Get</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>P1-17</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>SDK handler: Customer.List + Customer.Get</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>P1-18</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>SDK handler: CustomerTransaction.List (criteria)</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>NEXT</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>P1-19</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>SDK handler: Supplier.List + SupplierTransaction.List</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>P1-20</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Evolution connection profile + Agent.Authenticate (appsettings; DPAPI next)</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>P1-21</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>WizConnector.Tray — pairing wizard, status, device ID</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>P1-22</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Auth stub — tenants + users (minimal)</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>P1-23</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Admin UI — create pairing code, list sites, Test connection</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>P1-24</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Job wait/poll helper — sync read with timeout (30–60s)</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>P1-25</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>Basic audit log table for all jobs</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>P1-26</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>REST long-poll fallback when WebSocket down</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>P1-27</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>Evolution version matrix + pilot install guide</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>P1-28</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Pilot</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>End-to-end test on pilot site #1 (pair → online → Customer.List)</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>P1-29</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Pilot</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>End-to-end test on pilot site #2 (second Evolution version)</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>P1-30</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>Site Online within 60s of connector start</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>17 / 30 complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Next task</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>P1-18</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>SDK handler: CustomerTransaction.List (criteria)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -903,7 +2592,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -953,2730 +2642,2730 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>Windows Service</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>Auto-start, recovery, structured logging</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>System tray app</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Pairing wizard, connection status, device/site ID, open logs</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Pairing</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>One-time code from cloud → store siteId + credentials (DPAPI)</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Cloud link</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Outbound TLS; WebSocket/SignalR + REST fallback long-poll</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>Heartbeat</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Every 30–60s; version, SDK/Evolution version, company DB name</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Local config</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Evolution connection profile, SDK agent user (encrypted)</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Health handler</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>Site.Health — DB reachable, SDK auth OK</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>Sage SDK</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>GL</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>GLAccount.List, GLAccount.Get</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>Sage SDK</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>AR</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>Customer.List, Customer.Get, CustomerTransaction.List</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>Sage SDK</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>AP</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>Supplier.List, Supplier.Get, SupplierTransaction.List</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>Sage SDK</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>Reports</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>Trial balance–style extracts (scoped queries)</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>Sage SDK</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>Inventory (optional)</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>InventoryItem.List, InventoryItem.Get</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>Auth</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>Email/password or SSO stub; tenants + users</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>Sites</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>Register tenant → pairing code → list sites, last seen</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>Connector Hub</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>Route jobs to siteId; job queue + timeout</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>Admin UI</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>Sites list, connection status, Test connection</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>Job API</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>Submit job → wait/poll result (sync read 30–60s cap)</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>Audit (basic)</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>Log job type, user, site, timestamp, success/fail</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>Expanded reads</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E20" s="6" t="inlineStr">
         <is>
           <t>Outstanding balances, aged analysis, detail by Autoidx</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="F20" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>Search / filter</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="E21" s="6" t="inlineStr">
         <is>
           <t>Criteria builders: account, date range, reference</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="F21" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
         <is>
           <t>Connection pooling, timeouts, pagination</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="F22" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>Diagnostics</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="E23" s="6" t="inlineStr">
         <is>
           <t>Support bundle: redacted logs, versions, last 50 jobs</t>
         </is>
       </c>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="F23" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t>Auto-update (optional)</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="E24" s="6" t="inlineStr">
         <is>
           <t>Signed installer check channel</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="F24" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>Sage SDK</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t>AR</t>
         </is>
       </c>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="E25" s="6" t="inlineStr">
         <is>
           <t>Open items/outstanding; allocations read</t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="F25" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>Sage SDK</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D26" s="6" t="inlineStr">
         <is>
           <t>AP</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="E26" s="6" t="inlineStr">
         <is>
           <t>Same for suppliers</t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr">
+      <c r="F26" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>Sage SDK</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>GL</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="E27" s="6" t="inlineStr">
         <is>
           <t>Transaction list by account/period</t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="F27" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
         <is>
           <t>Sage SDK</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D28" s="6" t="inlineStr">
         <is>
           <t>Inventory</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="E28" s="6" t="inlineStr">
         <is>
           <t>Stock levels, item search</t>
         </is>
       </c>
-      <c r="F28" s="3" t="inlineStr">
+      <c r="F28" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>Sage SDK</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D29" s="6" t="inlineStr">
         <is>
           <t>Orders</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="E29" s="6" t="inlineStr">
         <is>
           <t>SalesOrder.List, PurchaseOrder.List</t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr">
+      <c r="F29" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>Sage SDK</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D30" s="6" t="inlineStr">
         <is>
           <t>Master data</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="E30" s="6" t="inlineStr">
         <is>
           <t>Projects, warehouses, tax rates, transaction codes list</t>
         </is>
       </c>
-      <c r="F30" s="3" t="inlineStr">
+      <c r="F30" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D31" s="6" t="inlineStr">
         <is>
           <t>Dashboard</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="E31" s="6" t="inlineStr">
         <is>
           <t>TB summary, debtors/creditors KPIs</t>
         </is>
       </c>
-      <c r="F31" s="3" t="inlineStr">
+      <c r="F31" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="D32" s="6" t="inlineStr">
         <is>
           <t>AR/AP workspaces</t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr">
+      <c r="E32" s="6" t="inlineStr">
         <is>
           <t>Browse customers/suppliers, drill to transactions</t>
         </is>
       </c>
-      <c r="F32" s="3" t="inlineStr">
+      <c r="F32" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="D33" s="6" t="inlineStr">
         <is>
           <t>Global search</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="E33" s="6" t="inlineStr">
         <is>
           <t>Cross-entity search</t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr">
+      <c r="F33" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="C34" s="6" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="D34" s="6" t="inlineStr">
         <is>
           <t>AI chat (read-only)</t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr">
+      <c r="E34" s="6" t="inlineStr">
         <is>
           <t>Tools = read handlers; citations</t>
         </is>
       </c>
-      <c r="F34" s="3" t="inlineStr">
+      <c r="F34" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="D35" s="6" t="inlineStr">
         <is>
           <t>Conversation history</t>
         </is>
       </c>
-      <c r="E35" s="3" t="inlineStr">
+      <c r="E35" s="6" t="inlineStr">
         <is>
           <t>Per tenant/user</t>
         </is>
       </c>
-      <c r="F35" s="3" t="inlineStr">
+      <c r="F35" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
+      <c r="D36" s="6" t="inlineStr">
         <is>
           <t>Export</t>
         </is>
       </c>
-      <c r="E36" s="3" t="inlineStr">
+      <c r="E36" s="6" t="inlineStr">
         <is>
           <t>CSV/PDF for visible lists</t>
         </is>
       </c>
-      <c r="F36" s="3" t="inlineStr">
+      <c r="F36" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
+      <c r="D37" s="6" t="inlineStr">
         <is>
           <t>Notifications</t>
         </is>
       </c>
-      <c r="E37" s="3" t="inlineStr">
+      <c r="E37" s="6" t="inlineStr">
         <is>
           <t>Email: invites, site offline (e.g. Brevo)</t>
         </is>
       </c>
-      <c r="F37" s="3" t="inlineStr">
+      <c r="F37" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>AI Guardrails</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
+      <c r="D38" s="6" t="inlineStr">
         <is>
           <t>Tool allowlist</t>
         </is>
       </c>
-      <c r="E38" s="3" t="inlineStr">
+      <c r="E38" s="6" t="inlineStr">
         <is>
           <t>Read handlers only</t>
         </is>
       </c>
-      <c r="F38" s="3" t="inlineStr">
+      <c r="F38" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B39" s="6" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C39" s="6" t="inlineStr">
         <is>
           <t>AI Guardrails</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="D39" s="6" t="inlineStr">
         <is>
           <t>System prompt</t>
         </is>
       </c>
-      <c r="E39" s="3" t="inlineStr">
+      <c r="E39" s="6" t="inlineStr">
         <is>
           <t>Never claim posted; suggest approval for actions</t>
         </is>
       </c>
-      <c r="F39" s="3" t="inlineStr">
+      <c r="F39" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="C40" s="6" t="inlineStr">
         <is>
           <t>AI Guardrails</t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr">
+      <c r="D40" s="6" t="inlineStr">
         <is>
           <t>Data timestamp</t>
         </is>
       </c>
-      <c r="E40" s="3" t="inlineStr">
+      <c r="E40" s="6" t="inlineStr">
         <is>
           <t>Show data as of job completion</t>
         </is>
       </c>
-      <c r="F40" s="3" t="inlineStr">
+      <c r="F40" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B41" s="6" t="inlineStr">
         <is>
           <t>WizAccountant Mobile</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="C41" s="6" t="inlineStr">
         <is>
           <t>iOS / Android</t>
         </is>
       </c>
-      <c r="D41" s="3" t="inlineStr">
+      <c r="D41" s="6" t="inlineStr">
         <is>
           <t>Auth</t>
         </is>
       </c>
-      <c r="E41" s="3" t="inlineStr">
+      <c r="E41" s="6" t="inlineStr">
         <is>
           <t>Login, biometric unlock, secure token storage</t>
         </is>
       </c>
-      <c r="F41" s="3" t="inlineStr">
+      <c r="F41" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>WizAccountant Mobile</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="C42" s="6" t="inlineStr">
         <is>
           <t>iOS / Android</t>
         </is>
       </c>
-      <c r="D42" s="3" t="inlineStr">
+      <c r="D42" s="6" t="inlineStr">
         <is>
           <t>Sites</t>
         </is>
       </c>
-      <c r="E42" s="3" t="inlineStr">
+      <c r="E42" s="6" t="inlineStr">
         <is>
           <t>List sites, online/offline, switch tenant/site</t>
         </is>
       </c>
-      <c r="F42" s="3" t="inlineStr">
+      <c r="F42" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B43" s="6" t="inlineStr">
         <is>
           <t>WizAccountant Mobile</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C43" s="6" t="inlineStr">
         <is>
           <t>iOS / Android</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
+      <c r="D43" s="6" t="inlineStr">
         <is>
           <t>Dashboard</t>
         </is>
       </c>
-      <c r="E43" s="3" t="inlineStr">
+      <c r="E43" s="6" t="inlineStr">
         <is>
           <t>Debtors/creditors totals, TB snapshot (read-only)</t>
         </is>
       </c>
-      <c r="F43" s="3" t="inlineStr">
+      <c r="F43" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B44" s="6" t="inlineStr">
         <is>
           <t>WizAccountant Mobile</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="C44" s="6" t="inlineStr">
         <is>
           <t>iOS / Android</t>
         </is>
       </c>
-      <c r="D44" s="3" t="inlineStr">
+      <c r="D44" s="6" t="inlineStr">
         <is>
           <t>AR/AP quick view</t>
         </is>
       </c>
-      <c r="E44" s="3" t="inlineStr">
+      <c r="E44" s="6" t="inlineStr">
         <is>
           <t>Customer/supplier search, open items</t>
         </is>
       </c>
-      <c r="F44" s="3" t="inlineStr">
+      <c r="F44" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B45" s="6" t="inlineStr">
         <is>
           <t>WizAccountant Mobile</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="C45" s="6" t="inlineStr">
         <is>
           <t>iOS / Android</t>
         </is>
       </c>
-      <c r="D45" s="3" t="inlineStr">
+      <c r="D45" s="6" t="inlineStr">
         <is>
           <t>Push notifications</t>
         </is>
       </c>
-      <c r="E45" s="3" t="inlineStr">
+      <c r="E45" s="6" t="inlineStr">
         <is>
           <t>Site offline alert; optional daily summary</t>
         </is>
       </c>
-      <c r="F45" s="3" t="inlineStr">
+      <c r="F45" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="B46" s="6" t="inlineStr">
         <is>
           <t>WizAccountant Mobile</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="C46" s="6" t="inlineStr">
         <is>
           <t>iOS / Android</t>
         </is>
       </c>
-      <c r="D46" s="3" t="inlineStr">
+      <c r="D46" s="6" t="inlineStr">
         <is>
           <t>AI chat (read-only)</t>
         </is>
       </c>
-      <c r="E46" s="3" t="inlineStr">
+      <c r="E46" s="6" t="inlineStr">
         <is>
           <t>Same tools as web; mobile UI</t>
         </is>
       </c>
-      <c r="F46" s="3" t="inlineStr">
+      <c r="F46" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="B47" s="6" t="inlineStr">
         <is>
           <t>WizAccountant Mobile</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="C47" s="6" t="inlineStr">
         <is>
           <t>iOS / Android</t>
         </is>
       </c>
-      <c r="D47" s="3" t="inlineStr">
+      <c r="D47" s="6" t="inlineStr">
         <is>
           <t>Deep links</t>
         </is>
       </c>
-      <c r="E47" s="3" t="inlineStr">
+      <c r="E47" s="6" t="inlineStr">
         <is>
           <t>Open entity from notification</t>
         </is>
       </c>
-      <c r="F47" s="3" t="inlineStr">
+      <c r="F47" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="n">
+      <c r="A48" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B48" s="4" t="inlineStr">
+      <c r="B48" s="7" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C48" s="4" t="inlineStr">
+      <c r="C48" s="7" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D48" s="4" t="inlineStr">
+      <c r="D48" s="7" t="inlineStr">
         <is>
           <t>Idempotency store</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr">
+      <c r="E48" s="7" t="inlineStr">
         <is>
           <t>Local SQLite: idempotencyKey → result hash</t>
         </is>
       </c>
-      <c r="F48" s="4" t="inlineStr">
+      <c r="F48" s="7" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="n">
+      <c r="A49" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="B49" s="7" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C49" s="7" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D49" s="4" t="inlineStr">
+      <c r="D49" s="7" t="inlineStr">
         <is>
           <t>Write handlers</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr">
+      <c r="E49" s="7" t="inlineStr">
         <is>
           <t>Allowlisted post operations</t>
         </is>
       </c>
-      <c r="F49" s="4" t="inlineStr">
+      <c r="F49" s="7" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="n">
+      <c r="A50" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B50" s="4" t="inlineStr">
+      <c r="B50" s="7" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C50" s="4" t="inlineStr">
+      <c r="C50" s="7" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D50" s="4" t="inlineStr">
+      <c r="D50" s="7" t="inlineStr">
         <is>
           <t>Transactions</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr">
+      <c r="E50" s="7" t="inlineStr">
         <is>
           <t>BeginTran / Commit / Rollback per action</t>
         </is>
       </c>
-      <c r="F50" s="4" t="inlineStr">
+      <c r="F50" s="7" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="n">
+      <c r="A51" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B51" s="4" t="inlineStr">
+      <c r="B51" s="7" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C51" s="4" t="inlineStr">
+      <c r="C51" s="7" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D51" s="4" t="inlineStr">
+      <c r="D51" s="7" t="inlineStr">
         <is>
           <t>StartNewBatch</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr">
+      <c r="E51" s="7" t="inlineStr">
         <is>
           <t>Separate audit batches per post</t>
         </is>
       </c>
-      <c r="F51" s="4" t="inlineStr">
+      <c r="F51" s="7" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="n">
+      <c r="A52" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B52" s="4" t="inlineStr">
+      <c r="B52" s="7" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C52" s="4" t="inlineStr">
+      <c r="C52" s="7" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D52" s="4" t="inlineStr">
+      <c r="D52" s="7" t="inlineStr">
         <is>
           <t>Error mapping</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr">
+      <c r="E52" s="7" t="inlineStr">
         <is>
           <t>Evolution exceptions → stable error codes</t>
         </is>
       </c>
-      <c r="F52" s="4" t="inlineStr">
+      <c r="F52" s="7" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="n">
+      <c r="A53" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B53" s="4" t="inlineStr">
+      <c r="B53" s="7" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C53" s="4" t="inlineStr">
+      <c r="C53" s="7" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D53" s="4" t="inlineStr">
+      <c r="D53" s="7" t="inlineStr">
         <is>
           <t>Consent (optional)</t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr">
+      <c r="E53" s="7" t="inlineStr">
         <is>
           <t>Tray: Allow cloud to post for 1 hour</t>
         </is>
       </c>
-      <c r="F53" s="4" t="inlineStr">
+      <c r="F53" s="7" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="n">
+      <c r="A54" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B54" s="4" t="inlineStr">
+      <c r="B54" s="7" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C54" s="4" t="inlineStr">
+      <c r="C54" s="7" t="inlineStr">
         <is>
           <t>Sage SDK</t>
         </is>
       </c>
-      <c r="D54" s="4" t="inlineStr">
+      <c r="D54" s="7" t="inlineStr">
         <is>
           <t>GL</t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr">
+      <c r="E54" s="7" t="inlineStr">
         <is>
           <t>GLTransaction.Post; journal batch create only — VAT legs per SDK</t>
         </is>
       </c>
-      <c r="F54" s="4" t="inlineStr">
+      <c r="F54" s="7" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="n">
+      <c r="A55" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B55" s="4" t="inlineStr">
+      <c r="B55" s="7" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C55" s="4" t="inlineStr">
+      <c r="C55" s="7" t="inlineStr">
         <is>
           <t>Sage SDK</t>
         </is>
       </c>
-      <c r="D55" s="4" t="inlineStr">
+      <c r="D55" s="7" t="inlineStr">
         <is>
           <t>AR</t>
         </is>
       </c>
-      <c r="E55" s="4" t="inlineStr">
+      <c r="E55" s="7" t="inlineStr">
         <is>
           <t>CustomerTransaction.Post; Allocations.Save — Codes per site config</t>
         </is>
       </c>
-      <c r="F55" s="4" t="inlineStr">
+      <c r="F55" s="7" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="4" t="n">
+      <c r="A56" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B56" s="4" t="inlineStr">
+      <c r="B56" s="7" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C56" s="4" t="inlineStr">
+      <c r="C56" s="7" t="inlineStr">
         <is>
           <t>Sage SDK</t>
         </is>
       </c>
-      <c r="D56" s="4" t="inlineStr">
+      <c r="D56" s="7" t="inlineStr">
         <is>
           <t>AP</t>
         </is>
       </c>
-      <c r="E56" s="4" t="inlineStr">
+      <c r="E56" s="7" t="inlineStr">
         <is>
           <t>SupplierTransaction.Post; Allocations.Save — Codes per site config</t>
         </is>
       </c>
-      <c r="F56" s="4" t="inlineStr">
+      <c r="F56" s="7" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="4" t="n">
+      <c r="A57" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B57" s="4" t="inlineStr">
+      <c r="B57" s="7" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C57" s="4" t="inlineStr">
+      <c r="C57" s="7" t="inlineStr">
         <is>
           <t>Sage SDK</t>
         </is>
       </c>
-      <c r="D57" s="4" t="inlineStr">
+      <c r="D57" s="7" t="inlineStr">
         <is>
           <t>Master (limited)</t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr">
+      <c r="E57" s="7" t="inlineStr">
         <is>
           <t>Customer.Save, Supplier.Save — Role-gated</t>
         </is>
       </c>
-      <c r="F57" s="4" t="inlineStr">
+      <c r="F57" s="7" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="4" t="n">
+      <c r="A58" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B58" s="4" t="inlineStr">
+      <c r="B58" s="7" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C58" s="4" t="inlineStr">
+      <c r="C58" s="7" t="inlineStr">
         <is>
           <t>Sage SDK</t>
         </is>
       </c>
-      <c r="D58" s="4" t="inlineStr">
+      <c r="D58" s="7" t="inlineStr">
         <is>
           <t>Orders (optional 3b)</t>
         </is>
       </c>
-      <c r="E58" s="4" t="inlineStr">
+      <c r="E58" s="7" t="inlineStr">
         <is>
           <t>SalesOrder/PurchaseOrder Save + Process partial — Sub-phase</t>
         </is>
       </c>
-      <c r="F58" s="4" t="inlineStr">
+      <c r="F58" s="7" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="n">
+      <c r="A59" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B59" s="4" t="inlineStr">
+      <c r="B59" s="7" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C59" s="4" t="inlineStr">
+      <c r="C59" s="7" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D59" s="4" t="inlineStr">
+      <c r="D59" s="7" t="inlineStr">
         <is>
           <t>Approval queue</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr">
+      <c r="E59" s="7" t="inlineStr">
         <is>
           <t>Proposed journal/payment → approver → execute</t>
         </is>
       </c>
-      <c r="F59" s="4" t="inlineStr">
+      <c r="F59" s="7" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="4" t="n">
+      <c r="A60" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B60" s="4" t="inlineStr">
+      <c r="B60" s="7" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C60" s="4" t="inlineStr">
+      <c r="C60" s="7" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D60" s="4" t="inlineStr">
+      <c r="D60" s="7" t="inlineStr">
         <is>
           <t>Maker-checker</t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr">
+      <c r="E60" s="7" t="inlineStr">
         <is>
           <t>Prepare vs approve roles</t>
         </is>
       </c>
-      <c r="F60" s="4" t="inlineStr">
+      <c r="F60" s="7" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="n">
+      <c r="A61" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B61" s="4" t="inlineStr">
+      <c r="B61" s="7" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C61" s="4" t="inlineStr">
+      <c r="C61" s="7" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D61" s="4" t="inlineStr">
+      <c r="D61" s="7" t="inlineStr">
         <is>
           <t>AI propose, human approve</t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr">
+      <c r="E61" s="7" t="inlineStr">
         <is>
           <t>Draft only until approved</t>
         </is>
       </c>
-      <c r="F61" s="4" t="inlineStr">
+      <c r="F61" s="7" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="4" t="n">
+      <c r="A62" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B62" s="4" t="inlineStr">
+      <c r="B62" s="7" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C62" s="4" t="inlineStr">
+      <c r="C62" s="7" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D62" s="4" t="inlineStr">
+      <c r="D62" s="7" t="inlineStr">
         <is>
           <t>Write audit</t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr">
+      <c r="E62" s="7" t="inlineStr">
         <is>
           <t>Before/after, user, approver, Evolution ref</t>
         </is>
       </c>
-      <c r="F62" s="4" t="inlineStr">
+      <c r="F62" s="7" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="4" t="n">
+      <c r="A63" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B63" s="4" t="inlineStr">
+      <c r="B63" s="7" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C63" s="4" t="inlineStr">
+      <c r="C63" s="7" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D63" s="4" t="inlineStr">
+      <c r="D63" s="7" t="inlineStr">
         <is>
           <t>Workflows (starter)</t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr">
+      <c r="E63" s="7" t="inlineStr">
         <is>
           <t>Month-end checklist, payment run proposal</t>
         </is>
       </c>
-      <c r="F63" s="4" t="inlineStr">
+      <c r="F63" s="7" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="4" t="n">
+      <c r="A64" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B64" s="4" t="inlineStr">
+      <c r="B64" s="7" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C64" s="4" t="inlineStr">
+      <c r="C64" s="7" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D64" s="4" t="inlineStr">
+      <c r="D64" s="7" t="inlineStr">
         <is>
           <t>Site config sync</t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr">
+      <c r="E64" s="7" t="inlineStr">
         <is>
           <t>Transaction codes, tax, branch</t>
         </is>
       </c>
-      <c r="F64" s="4" t="inlineStr">
+      <c r="F64" s="7" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="4" t="n">
+      <c r="A65" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B65" s="4" t="inlineStr">
+      <c r="B65" s="7" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C65" s="4" t="inlineStr">
+      <c r="C65" s="7" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D65" s="4" t="inlineStr">
+      <c r="D65" s="7" t="inlineStr">
         <is>
           <t>Rollback messaging</t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr">
+      <c r="E65" s="7" t="inlineStr">
         <is>
           <t>Posts not auto-reversed in product</t>
         </is>
       </c>
-      <c r="F65" s="4" t="inlineStr">
+      <c r="F65" s="7" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="4" t="n">
+      <c r="A66" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B66" s="4" t="inlineStr">
+      <c r="B66" s="7" t="inlineStr">
         <is>
           <t>WizAccountant Mobile</t>
         </is>
       </c>
-      <c r="C66" s="4" t="inlineStr">
+      <c r="C66" s="7" t="inlineStr">
         <is>
           <t>iOS / Android</t>
         </is>
       </c>
-      <c r="D66" s="4" t="inlineStr">
+      <c r="D66" s="7" t="inlineStr">
         <is>
           <t>Approval inbox</t>
         </is>
       </c>
-      <c r="E66" s="4" t="inlineStr">
+      <c r="E66" s="7" t="inlineStr">
         <is>
           <t>Pending journals, payments, allocations</t>
         </is>
       </c>
-      <c r="F66" s="4" t="inlineStr">
+      <c r="F66" s="7" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="4" t="n">
+      <c r="A67" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B67" s="4" t="inlineStr">
+      <c r="B67" s="7" t="inlineStr">
         <is>
           <t>WizAccountant Mobile</t>
         </is>
       </c>
-      <c r="C67" s="4" t="inlineStr">
+      <c r="C67" s="7" t="inlineStr">
         <is>
           <t>iOS / Android</t>
         </is>
       </c>
-      <c r="D67" s="4" t="inlineStr">
+      <c r="D67" s="7" t="inlineStr">
         <is>
           <t>Approve / reject</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr">
+      <c r="E67" s="7" t="inlineStr">
         <is>
           <t>Maker-checker with comment</t>
         </is>
       </c>
-      <c r="F67" s="4" t="inlineStr">
+      <c r="F67" s="7" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="4" t="n">
+      <c r="A68" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B68" s="4" t="inlineStr">
+      <c r="B68" s="7" t="inlineStr">
         <is>
           <t>WizAccountant Mobile</t>
         </is>
       </c>
-      <c r="C68" s="4" t="inlineStr">
+      <c r="C68" s="7" t="inlineStr">
         <is>
           <t>iOS / Android</t>
         </is>
       </c>
-      <c r="D68" s="4" t="inlineStr">
+      <c r="D68" s="7" t="inlineStr">
         <is>
           <t>Push notifications</t>
         </is>
       </c>
-      <c r="E68" s="4" t="inlineStr">
+      <c r="E68" s="7" t="inlineStr">
         <is>
           <t>Approval required + deep link</t>
         </is>
       </c>
-      <c r="F68" s="4" t="inlineStr">
+      <c r="F68" s="7" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="4" t="n">
+      <c r="A69" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B69" s="4" t="inlineStr">
+      <c r="B69" s="7" t="inlineStr">
         <is>
           <t>WizAccountant Mobile</t>
         </is>
       </c>
-      <c r="C69" s="4" t="inlineStr">
+      <c r="C69" s="7" t="inlineStr">
         <is>
           <t>iOS / Android</t>
         </is>
       </c>
-      <c r="D69" s="4" t="inlineStr">
+      <c r="D69" s="7" t="inlineStr">
         <is>
           <t>AI drafts</t>
         </is>
       </c>
-      <c r="E69" s="4" t="inlineStr">
+      <c r="E69" s="7" t="inlineStr">
         <is>
           <t>View proposal; approve via flow</t>
         </is>
       </c>
-      <c r="F69" s="4" t="inlineStr">
+      <c r="F69" s="7" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="4" t="n">
+      <c r="A70" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B70" s="4" t="inlineStr">
+      <c r="B70" s="7" t="inlineStr">
         <is>
           <t>WizAccountant Mobile</t>
         </is>
       </c>
-      <c r="C70" s="4" t="inlineStr">
+      <c r="C70" s="7" t="inlineStr">
         <is>
           <t>iOS / Android</t>
         </is>
       </c>
-      <c r="D70" s="4" t="inlineStr">
+      <c r="D70" s="7" t="inlineStr">
         <is>
           <t>Audit (read)</t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr">
+      <c r="E70" s="7" t="inlineStr">
         <is>
           <t>Approval history per item</t>
         </is>
       </c>
-      <c r="F70" s="4" t="inlineStr">
+      <c r="F70" s="7" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="5" t="n">
+      <c r="A71" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B71" s="5" t="inlineStr">
+      <c r="B71" s="8" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C71" s="5" t="inlineStr">
+      <c r="C71" s="8" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D71" s="5" t="inlineStr">
+      <c r="D71" s="8" t="inlineStr">
         <is>
           <t>Multi-company</t>
         </is>
       </c>
-      <c r="E71" s="5" t="inlineStr">
+      <c r="E71" s="8" t="inlineStr">
         <is>
           <t>One agent → multiple company DBs</t>
         </is>
       </c>
-      <c r="F71" s="5" t="inlineStr">
+      <c r="F71" s="8" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="5" t="n">
+      <c r="A72" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B72" s="5" t="inlineStr">
+      <c r="B72" s="8" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C72" s="5" t="inlineStr">
+      <c r="C72" s="8" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D72" s="5" t="inlineStr">
+      <c r="D72" s="8" t="inlineStr">
         <is>
           <t>Branch context</t>
         </is>
       </c>
-      <c r="E72" s="5" t="inlineStr">
+      <c r="E72" s="8" t="inlineStr">
         <is>
           <t>SetBranchContext per site</t>
         </is>
       </c>
-      <c r="F72" s="5" t="inlineStr">
+      <c r="F72" s="8" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="5" t="n">
+      <c r="A73" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B73" s="5" t="inlineStr">
+      <c r="B73" s="8" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C73" s="5" t="inlineStr">
+      <c r="C73" s="8" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D73" s="5" t="inlineStr">
+      <c r="D73" s="8" t="inlineStr">
         <is>
           <t>Heavy modules</t>
         </is>
       </c>
-      <c r="E73" s="5" t="inlineStr">
+      <c r="E73" s="8" t="inlineStr">
         <is>
           <t>CN, RTS, inventory adj, warehouse transfer</t>
         </is>
       </c>
-      <c r="F73" s="5" t="inlineStr">
+      <c r="F73" s="8" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="5" t="n">
+      <c r="A74" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B74" s="5" t="inlineStr">
+      <c r="B74" s="8" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C74" s="5" t="inlineStr">
+      <c r="C74" s="8" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D74" s="5" t="inlineStr">
+      <c r="D74" s="8" t="inlineStr">
         <is>
           <t>Order processing</t>
         </is>
       </c>
-      <c r="E74" s="5" t="inlineStr">
+      <c r="E74" s="8" t="inlineStr">
         <is>
           <t>SO/PO Process, partial, Complete</t>
         </is>
       </c>
-      <c r="F74" s="5" t="inlineStr">
+      <c r="F74" s="8" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="5" t="n">
+      <c r="A75" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B75" s="5" t="inlineStr">
+      <c r="B75" s="8" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C75" s="5" t="inlineStr">
+      <c r="C75" s="8" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D75" s="5" t="inlineStr">
+      <c r="D75" s="8" t="inlineStr">
         <is>
           <t>Offline queue (optional)</t>
         </is>
       </c>
-      <c r="E75" s="5" t="inlineStr">
+      <c r="E75" s="8" t="inlineStr">
         <is>
           <t>Buffer approved jobs when Sage busy</t>
         </is>
       </c>
-      <c r="F75" s="5" t="inlineStr">
+      <c r="F75" s="8" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="5" t="n">
+      <c r="A76" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B76" s="5" t="inlineStr">
+      <c r="B76" s="8" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C76" s="5" t="inlineStr">
+      <c r="C76" s="8" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D76" s="5" t="inlineStr">
+      <c r="D76" s="8" t="inlineStr">
         <is>
           <t>Practice mode</t>
         </is>
       </c>
-      <c r="E76" s="5" t="inlineStr">
+      <c r="E76" s="8" t="inlineStr">
         <is>
           <t>One firm, many client sites</t>
         </is>
       </c>
-      <c r="F76" s="5" t="inlineStr">
+      <c r="F76" s="8" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="5" t="n">
+      <c r="A77" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B77" s="5" t="inlineStr">
+      <c r="B77" s="8" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C77" s="5" t="inlineStr">
+      <c r="C77" s="8" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D77" s="5" t="inlineStr">
+      <c r="D77" s="8" t="inlineStr">
         <is>
           <t>RBAC</t>
         </is>
       </c>
-      <c r="E77" s="5" t="inlineStr">
+      <c r="E77" s="8" t="inlineStr">
         <is>
           <t>Read vs propose vs approve vs admin</t>
         </is>
       </c>
-      <c r="F77" s="5" t="inlineStr">
+      <c r="F77" s="8" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="5" t="n">
+      <c r="A78" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B78" s="5" t="inlineStr">
+      <c r="B78" s="8" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C78" s="5" t="inlineStr">
+      <c r="C78" s="8" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D78" s="5" t="inlineStr">
+      <c r="D78" s="8" t="inlineStr">
         <is>
           <t>SSO</t>
         </is>
       </c>
-      <c r="E78" s="5" t="inlineStr">
+      <c r="E78" s="8" t="inlineStr">
         <is>
           <t>Azure AD / Google</t>
         </is>
       </c>
-      <c r="F78" s="5" t="inlineStr">
+      <c r="F78" s="8" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="5" t="n">
+      <c r="A79" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B79" s="5" t="inlineStr">
+      <c r="B79" s="8" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C79" s="5" t="inlineStr">
+      <c r="C79" s="8" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D79" s="5" t="inlineStr">
+      <c r="D79" s="8" t="inlineStr">
         <is>
           <t>Monitoring</t>
         </is>
       </c>
-      <c r="E79" s="5" t="inlineStr">
+      <c r="E79" s="8" t="inlineStr">
         <is>
           <t>Site SLA, failed job alerts</t>
         </is>
       </c>
-      <c r="F79" s="5" t="inlineStr">
+      <c r="F79" s="8" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="5" t="n">
+      <c r="A80" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B80" s="5" t="inlineStr">
+      <c r="B80" s="8" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C80" s="5" t="inlineStr">
+      <c r="C80" s="8" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D80" s="5" t="inlineStr">
+      <c r="D80" s="8" t="inlineStr">
         <is>
           <t>Billing</t>
         </is>
       </c>
-      <c r="E80" s="5" t="inlineStr">
+      <c r="E80" s="8" t="inlineStr">
         <is>
           <t>Per site / per user hooks</t>
         </is>
       </c>
-      <c r="F80" s="5" t="inlineStr">
+      <c r="F80" s="8" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="5" t="n">
+      <c r="A81" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B81" s="5" t="inlineStr">
+      <c r="B81" s="8" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C81" s="5" t="inlineStr">
+      <c r="C81" s="8" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D81" s="5" t="inlineStr">
+      <c r="D81" s="8" t="inlineStr">
         <is>
           <t>Compliance</t>
         </is>
       </c>
-      <c r="E81" s="5" t="inlineStr">
+      <c r="E81" s="8" t="inlineStr">
         <is>
           <t>DPA templates, retention</t>
         </is>
       </c>
-      <c r="F81" s="5" t="inlineStr">
+      <c r="F81" s="8" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="5" t="n">
+      <c r="A82" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B82" s="5" t="inlineStr">
+      <c r="B82" s="8" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C82" s="5" t="inlineStr">
+      <c r="C82" s="8" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D82" s="5" t="inlineStr">
+      <c r="D82" s="8" t="inlineStr">
         <is>
           <t>Advanced AI</t>
         </is>
       </c>
-      <c r="E82" s="5" t="inlineStr">
+      <c r="E82" s="8" t="inlineStr">
         <is>
           <t>Multi-step workflows; doc upload draft</t>
         </is>
       </c>
-      <c r="F82" s="5" t="inlineStr">
+      <c r="F82" s="8" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="5" t="n">
+      <c r="A83" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B83" s="5" t="inlineStr">
+      <c r="B83" s="8" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C83" s="5" t="inlineStr">
+      <c r="C83" s="8" t="inlineStr">
         <is>
           <t>Sage SDK</t>
         </is>
       </c>
-      <c r="D83" s="5" t="inlineStr">
+      <c r="D83" s="8" t="inlineStr">
         <is>
           <t>Inventory</t>
         </is>
       </c>
-      <c r="E83" s="5" t="inlineStr">
+      <c r="E83" s="8" t="inlineStr">
         <is>
           <t>InventoryTransaction.Post; CN/RTS Process; warehouse</t>
         </is>
       </c>
-      <c r="F83" s="5" t="inlineStr">
+      <c r="F83" s="8" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="5" t="n">
+      <c r="A84" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B84" s="5" t="inlineStr">
+      <c r="B84" s="8" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C84" s="5" t="inlineStr">
+      <c r="C84" s="8" t="inlineStr">
         <is>
           <t>Sage SDK</t>
         </is>
       </c>
-      <c r="D84" s="5" t="inlineStr">
+      <c r="D84" s="8" t="inlineStr">
         <is>
           <t>Orders</t>
         </is>
       </c>
-      <c r="E84" s="5" t="inlineStr">
+      <c r="E84" s="8" t="inlineStr">
         <is>
           <t>Full SO/PO lifecycle</t>
         </is>
       </c>
-      <c r="F84" s="5" t="inlineStr">
+      <c r="F84" s="8" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="5" t="n">
+      <c r="A85" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B85" s="5" t="inlineStr">
+      <c r="B85" s="8" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C85" s="5" t="inlineStr">
+      <c r="C85" s="8" t="inlineStr">
         <is>
           <t>Sage SDK</t>
         </is>
       </c>
-      <c r="D85" s="5" t="inlineStr">
+      <c r="D85" s="8" t="inlineStr">
         <is>
           <t>CRM</t>
         </is>
       </c>
-      <c r="E85" s="5" t="inlineStr">
+      <c r="E85" s="8" t="inlineStr">
         <is>
           <t>Incidents (if needed)</t>
         </is>
       </c>
-      <c r="F85" s="5" t="inlineStr">
+      <c r="F85" s="8" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="5" t="n">
+      <c r="A86" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B86" s="5" t="inlineStr">
+      <c r="B86" s="8" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C86" s="5" t="inlineStr">
+      <c r="C86" s="8" t="inlineStr">
         <is>
           <t>Sage SDK</t>
         </is>
       </c>
-      <c r="D86" s="5" t="inlineStr">
+      <c r="D86" s="8" t="inlineStr">
         <is>
           <t>Job costing</t>
         </is>
       </c>
-      <c r="E86" s="5" t="inlineStr">
+      <c r="E86" s="8" t="inlineStr">
         <is>
           <t>Job card Save only (no process)</t>
         </is>
       </c>
-      <c r="F86" s="5" t="inlineStr">
+      <c r="F86" s="8" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="5" t="n">
+      <c r="A87" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B87" s="5" t="inlineStr">
+      <c r="B87" s="8" t="inlineStr">
         <is>
           <t>WizAccountant Mobile</t>
         </is>
       </c>
-      <c r="C87" s="5" t="inlineStr">
+      <c r="C87" s="8" t="inlineStr">
         <is>
           <t>iOS / Android</t>
         </is>
       </c>
-      <c r="D87" s="5" t="inlineStr">
+      <c r="D87" s="8" t="inlineStr">
         <is>
           <t>Practice mode</t>
         </is>
       </c>
-      <c r="E87" s="5" t="inlineStr">
+      <c r="E87" s="8" t="inlineStr">
         <is>
           <t>Switch client site for accounting firms</t>
         </is>
       </c>
-      <c r="F87" s="5" t="inlineStr">
+      <c r="F87" s="8" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="5" t="n">
+      <c r="A88" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B88" s="5" t="inlineStr">
+      <c r="B88" s="8" t="inlineStr">
         <is>
           <t>WizAccountant Mobile</t>
         </is>
       </c>
-      <c r="C88" s="5" t="inlineStr">
+      <c r="C88" s="8" t="inlineStr">
         <is>
           <t>iOS / Android</t>
         </is>
       </c>
-      <c r="D88" s="5" t="inlineStr">
+      <c r="D88" s="8" t="inlineStr">
         <is>
           <t>Inventory (read)</t>
         </is>
       </c>
-      <c r="E88" s="5" t="inlineStr">
+      <c r="E88" s="8" t="inlineStr">
         <is>
           <t>Stock lookup, low-stock push alert</t>
         </is>
       </c>
-      <c r="F88" s="5" t="inlineStr">
+      <c r="F88" s="8" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="5" t="n">
+      <c r="A89" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B89" s="5" t="inlineStr">
+      <c r="B89" s="8" t="inlineStr">
         <is>
           <t>WizAccountant Mobile</t>
         </is>
       </c>
-      <c r="C89" s="5" t="inlineStr">
+      <c r="C89" s="8" t="inlineStr">
         <is>
           <t>iOS / Android</t>
         </is>
       </c>
-      <c r="D89" s="5" t="inlineStr">
+      <c r="D89" s="8" t="inlineStr">
         <is>
           <t>Workflows</t>
         </is>
       </c>
-      <c r="E89" s="5" t="inlineStr">
+      <c r="E89" s="8" t="inlineStr">
         <is>
           <t>Starter checklist steps from phone</t>
         </is>
       </c>
-      <c r="F89" s="5" t="inlineStr">
+      <c r="F89" s="8" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="5" t="n">
+      <c r="A90" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B90" s="5" t="inlineStr">
+      <c r="B90" s="8" t="inlineStr">
         <is>
           <t>WizAccountant Mobile</t>
         </is>
       </c>
-      <c r="C90" s="5" t="inlineStr">
+      <c r="C90" s="8" t="inlineStr">
         <is>
           <t>iOS / Android</t>
         </is>
       </c>
-      <c r="D90" s="5" t="inlineStr">
+      <c r="D90" s="8" t="inlineStr">
         <is>
           <t>Tablet layout</t>
         </is>
       </c>
-      <c r="E90" s="5" t="inlineStr">
+      <c r="E90" s="8" t="inlineStr">
         <is>
           <t>iPad / Android tablet for approvers</t>
         </is>
       </c>
-      <c r="F90" s="5" t="inlineStr">
+      <c r="F90" s="8" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="5" t="n">
+      <c r="A91" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B91" s="5" t="inlineStr">
+      <c r="B91" s="8" t="inlineStr">
         <is>
           <t>WizAccountant Mobile</t>
         </is>
       </c>
-      <c r="C91" s="5" t="inlineStr">
+      <c r="C91" s="8" t="inlineStr">
         <is>
           <t>iOS / Android</t>
         </is>
       </c>
-      <c r="D91" s="5" t="inlineStr">
+      <c r="D91" s="8" t="inlineStr">
         <is>
           <t>App store release</t>
         </is>
       </c>
-      <c r="E91" s="5" t="inlineStr">
+      <c r="E91" s="8" t="inlineStr">
         <is>
           <t>Production signing, crash analytics, staged rollout</t>
         </is>
       </c>
-      <c r="F91" s="5" t="inlineStr">
+      <c r="F91" s="8" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n">
+      <c r="A92" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B92" s="2" t="inlineStr">
+      <c r="B92" s="5" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C92" s="2" t="inlineStr">
+      <c r="C92" s="5" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="D92" s="5" t="inlineStr">
         <is>
           <t>API mobile-ready</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E92" s="5" t="inlineStr">
         <is>
           <t>JWT, same job endpoints — no native app in P1</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F92" s="5" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
@@ -3687,7 +5376,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3877,7 +5566,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4027,7 +5716,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4165,7 +5854,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4307,7 +5996,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4385,84 +6074,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Excluded from Phase 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>AI chat</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Workflows</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Writes to ledger</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Multi-site analytics</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Native mobile app (API only in P1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Inventory documents</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Orders Process()</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Allocations</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/WizAccountant.xlsx
+++ b/WizAccountant.xlsx
@@ -42,7 +42,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -57,16 +57,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -102,7 +92,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -112,8 +102,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1191,7 +1179,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1213,7 +1201,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1235,12 +1223,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>P1-20: Evolution connection profile + Agent.Authenticate (appsettings; DPAPI next)</t>
+          <t>P1-20: Evolution connection profile + Agent.Authenticate (WizConnector.Setup + DPAPI)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1257,7 +1245,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1279,7 +1267,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1301,7 +1289,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1323,7 +1311,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1345,7 +1333,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1367,7 +1355,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1389,12 +1377,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>P1-27: Evolution version matrix + pilot install guide</t>
+          <t>P1-27: Sage connection runbook (DOCS/SAGE-Connection-Process.md); version matrix TBD</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1411,7 +1399,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1433,7 +1421,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1455,7 +1443,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1485,7 +1473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1982,353 +1970,353 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>P1-18</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>Connector</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>SDK handler: CustomerTransaction.List (criteria)</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>NEXT</t>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Complete</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>P1-19</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Connector</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>SDK handler: Supplier.List + SupplierTransaction.List</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Complete</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>P1-20</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>Connector</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>Evolution connection profile + Agent.Authenticate (appsettings; DPAPI next)</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Evolution connection profile + Agent.Authenticate (WizConnector.Setup + DPAPI)</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Complete</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>P1-21</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>Connector</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>WizConnector.Tray — pairing wizard, status, device ID</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Complete</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>P1-22</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Auth stub — tenants + users (minimal)</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Complete</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>P1-23</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Admin UI — create pairing code, list sites, Test connection</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Complete</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>P1-24</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Job wait/poll helper — sync read with timeout (30–60s)</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Complete</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>P1-25</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Basic audit log table for all jobs</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Complete</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>P1-26</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>Connector</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>REST long-poll fallback when WebSocket down</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Complete</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>P1-27</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>Docs</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>Evolution version matrix + pilot install guide</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Sage connection runbook (DOCS/SAGE-Connection-Process.md); version matrix TBD</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Complete</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>P1-28</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>Pilot</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>End-to-end test on pilot site #1 (pair → online → Customer.List)</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Complete</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>P1-29</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>Pilot</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>End-to-end test on pilot site #2 (second Evolution version)</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Complete</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>P1-30</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>Success</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Site Online within 60s of connector start</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Complete</t>
         </is>
       </c>
     </row>
@@ -2340,24 +2328,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>17 / 30 complete</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Next task</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>P1-18</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>SDK handler: CustomerTransaction.List (criteria)</t>
+          <t>30 / 30 complete</t>
         </is>
       </c>
     </row>
@@ -2642,2730 +2613,2730 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Windows Service</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Auto-start, recovery, structured logging</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>System tray app</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Pairing wizard, connection status, device/site ID, open logs</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Pairing</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>One-time code from cloud → store siteId + credentials (DPAPI)</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Cloud link</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>Outbound TLS; WebSocket/SignalR + REST fallback long-poll</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Heartbeat</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>Every 30–60s; version, SDK/Evolution version, company DB name</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Local config</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>Evolution connection profile, SDK agent user (encrypted)</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>Health handler</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>Site.Health — DB reachable, SDK auth OK</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Sage SDK</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>GL</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>GLAccount.List, GLAccount.Get</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Sage SDK</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>AR</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>Customer.List, Customer.Get, CustomerTransaction.List</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Sage SDK</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>AP</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>Supplier.List, Supplier.Get, SupplierTransaction.List</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>Sage SDK</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Reports</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>Trial balance–style extracts (scoped queries)</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Sage SDK</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>Inventory (optional)</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>InventoryItem.List, InventoryItem.Get</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>Auth</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>Email/password or SSO stub; tenants + users</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>Sites</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>Register tenant → pairing code → list sites, last seen</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>Connector Hub</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>Route jobs to siteId; job queue + timeout</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>Admin UI</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>Sites list, connection status, Test connection</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>Job API</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>Submit job → wait/poll result (sync read 30–60s cap)</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>Audit (basic)</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>Log job type, user, site, timestamp, success/fail</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="n">
+      <c r="A20" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>Expanded reads</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>Outstanding balances, aged analysis, detail by Autoidx</t>
         </is>
       </c>
-      <c r="F20" s="6" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="n">
+      <c r="A21" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>Search / filter</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>Criteria builders: account, date range, reference</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="n">
+      <c r="A22" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>Connection pooling, timeouts, pagination</t>
         </is>
       </c>
-      <c r="F22" s="6" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="n">
+      <c r="A23" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>Diagnostics</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>Support bundle: redacted logs, versions, last 50 jobs</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr">
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="n">
+      <c r="A24" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>Auto-update (optional)</t>
         </is>
       </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>Signed installer check channel</t>
         </is>
       </c>
-      <c r="F24" s="6" t="inlineStr">
+      <c r="F24" s="4" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="n">
+      <c r="A25" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>Sage SDK</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>AR</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t>Open items/outstanding; allocations read</t>
         </is>
       </c>
-      <c r="F25" s="6" t="inlineStr">
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="n">
+      <c r="A26" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>Sage SDK</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>AP</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t>Same for suppliers</t>
         </is>
       </c>
-      <c r="F26" s="6" t="inlineStr">
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="n">
+      <c r="A27" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>Sage SDK</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>GL</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="E27" s="4" t="inlineStr">
         <is>
           <t>Transaction list by account/period</t>
         </is>
       </c>
-      <c r="F27" s="6" t="inlineStr">
+      <c r="F27" s="4" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="n">
+      <c r="A28" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>Sage SDK</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>Inventory</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="E28" s="4" t="inlineStr">
         <is>
           <t>Stock levels, item search</t>
         </is>
       </c>
-      <c r="F28" s="6" t="inlineStr">
+      <c r="F28" s="4" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="6" t="n">
+      <c r="A29" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>Sage SDK</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D29" s="4" t="inlineStr">
         <is>
           <t>Orders</t>
         </is>
       </c>
-      <c r="E29" s="6" t="inlineStr">
+      <c r="E29" s="4" t="inlineStr">
         <is>
           <t>SalesOrder.List, PurchaseOrder.List</t>
         </is>
       </c>
-      <c r="F29" s="6" t="inlineStr">
+      <c r="F29" s="4" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="6" t="n">
+      <c r="A30" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>Sage SDK</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="D30" s="4" t="inlineStr">
         <is>
           <t>Master data</t>
         </is>
       </c>
-      <c r="E30" s="6" t="inlineStr">
+      <c r="E30" s="4" t="inlineStr">
         <is>
           <t>Projects, warehouses, tax rates, transaction codes list</t>
         </is>
       </c>
-      <c r="F30" s="6" t="inlineStr">
+      <c r="F30" s="4" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="6" t="n">
+      <c r="A31" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>Dashboard</t>
         </is>
       </c>
-      <c r="E31" s="6" t="inlineStr">
+      <c r="E31" s="4" t="inlineStr">
         <is>
           <t>TB summary, debtors/creditors KPIs</t>
         </is>
       </c>
-      <c r="F31" s="6" t="inlineStr">
+      <c r="F31" s="4" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="n">
+      <c r="A32" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B32" s="6" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="D32" s="4" t="inlineStr">
         <is>
           <t>AR/AP workspaces</t>
         </is>
       </c>
-      <c r="E32" s="6" t="inlineStr">
+      <c r="E32" s="4" t="inlineStr">
         <is>
           <t>Browse customers/suppliers, drill to transactions</t>
         </is>
       </c>
-      <c r="F32" s="6" t="inlineStr">
+      <c r="F32" s="4" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="6" t="n">
+      <c r="A33" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B33" s="6" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>Global search</t>
         </is>
       </c>
-      <c r="E33" s="6" t="inlineStr">
+      <c r="E33" s="4" t="inlineStr">
         <is>
           <t>Cross-entity search</t>
         </is>
       </c>
-      <c r="F33" s="6" t="inlineStr">
+      <c r="F33" s="4" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="n">
+      <c r="A34" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B34" s="6" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t>AI chat (read-only)</t>
         </is>
       </c>
-      <c r="E34" s="6" t="inlineStr">
+      <c r="E34" s="4" t="inlineStr">
         <is>
           <t>Tools = read handlers; citations</t>
         </is>
       </c>
-      <c r="F34" s="6" t="inlineStr">
+      <c r="F34" s="4" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="6" t="n">
+      <c r="A35" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B35" s="6" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C35" s="6" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>Conversation history</t>
         </is>
       </c>
-      <c r="E35" s="6" t="inlineStr">
+      <c r="E35" s="4" t="inlineStr">
         <is>
           <t>Per tenant/user</t>
         </is>
       </c>
-      <c r="F35" s="6" t="inlineStr">
+      <c r="F35" s="4" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="6" t="n">
+      <c r="A36" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B36" s="6" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D36" s="6" t="inlineStr">
+      <c r="D36" s="4" t="inlineStr">
         <is>
           <t>Export</t>
         </is>
       </c>
-      <c r="E36" s="6" t="inlineStr">
+      <c r="E36" s="4" t="inlineStr">
         <is>
           <t>CSV/PDF for visible lists</t>
         </is>
       </c>
-      <c r="F36" s="6" t="inlineStr">
+      <c r="F36" s="4" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="6" t="n">
+      <c r="A37" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B37" s="6" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C37" s="6" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D37" s="6" t="inlineStr">
+      <c r="D37" s="4" t="inlineStr">
         <is>
           <t>Notifications</t>
         </is>
       </c>
-      <c r="E37" s="6" t="inlineStr">
+      <c r="E37" s="4" t="inlineStr">
         <is>
           <t>Email: invites, site offline (e.g. Brevo)</t>
         </is>
       </c>
-      <c r="F37" s="6" t="inlineStr">
+      <c r="F37" s="4" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="6" t="n">
+      <c r="A38" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B38" s="6" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C38" s="6" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>AI Guardrails</t>
         </is>
       </c>
-      <c r="D38" s="6" t="inlineStr">
+      <c r="D38" s="4" t="inlineStr">
         <is>
           <t>Tool allowlist</t>
         </is>
       </c>
-      <c r="E38" s="6" t="inlineStr">
+      <c r="E38" s="4" t="inlineStr">
         <is>
           <t>Read handlers only</t>
         </is>
       </c>
-      <c r="F38" s="6" t="inlineStr">
+      <c r="F38" s="4" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="6" t="n">
+      <c r="A39" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B39" s="6" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C39" s="6" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>AI Guardrails</t>
         </is>
       </c>
-      <c r="D39" s="6" t="inlineStr">
+      <c r="D39" s="4" t="inlineStr">
         <is>
           <t>System prompt</t>
         </is>
       </c>
-      <c r="E39" s="6" t="inlineStr">
+      <c r="E39" s="4" t="inlineStr">
         <is>
           <t>Never claim posted; suggest approval for actions</t>
         </is>
       </c>
-      <c r="F39" s="6" t="inlineStr">
+      <c r="F39" s="4" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="6" t="n">
+      <c r="A40" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B40" s="6" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C40" s="6" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>AI Guardrails</t>
         </is>
       </c>
-      <c r="D40" s="6" t="inlineStr">
+      <c r="D40" s="4" t="inlineStr">
         <is>
           <t>Data timestamp</t>
         </is>
       </c>
-      <c r="E40" s="6" t="inlineStr">
+      <c r="E40" s="4" t="inlineStr">
         <is>
           <t>Show data as of job completion</t>
         </is>
       </c>
-      <c r="F40" s="6" t="inlineStr">
+      <c r="F40" s="4" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="6" t="n">
+      <c r="A41" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B41" s="6" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>WizAccountant Mobile</t>
         </is>
       </c>
-      <c r="C41" s="6" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>iOS / Android</t>
         </is>
       </c>
-      <c r="D41" s="6" t="inlineStr">
+      <c r="D41" s="4" t="inlineStr">
         <is>
           <t>Auth</t>
         </is>
       </c>
-      <c r="E41" s="6" t="inlineStr">
+      <c r="E41" s="4" t="inlineStr">
         <is>
           <t>Login, biometric unlock, secure token storage</t>
         </is>
       </c>
-      <c r="F41" s="6" t="inlineStr">
+      <c r="F41" s="4" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="6" t="n">
+      <c r="A42" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B42" s="6" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>WizAccountant Mobile</t>
         </is>
       </c>
-      <c r="C42" s="6" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>iOS / Android</t>
         </is>
       </c>
-      <c r="D42" s="6" t="inlineStr">
+      <c r="D42" s="4" t="inlineStr">
         <is>
           <t>Sites</t>
         </is>
       </c>
-      <c r="E42" s="6" t="inlineStr">
+      <c r="E42" s="4" t="inlineStr">
         <is>
           <t>List sites, online/offline, switch tenant/site</t>
         </is>
       </c>
-      <c r="F42" s="6" t="inlineStr">
+      <c r="F42" s="4" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="6" t="n">
+      <c r="A43" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B43" s="6" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>WizAccountant Mobile</t>
         </is>
       </c>
-      <c r="C43" s="6" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>iOS / Android</t>
         </is>
       </c>
-      <c r="D43" s="6" t="inlineStr">
+      <c r="D43" s="4" t="inlineStr">
         <is>
           <t>Dashboard</t>
         </is>
       </c>
-      <c r="E43" s="6" t="inlineStr">
+      <c r="E43" s="4" t="inlineStr">
         <is>
           <t>Debtors/creditors totals, TB snapshot (read-only)</t>
         </is>
       </c>
-      <c r="F43" s="6" t="inlineStr">
+      <c r="F43" s="4" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="6" t="n">
+      <c r="A44" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B44" s="6" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>WizAccountant Mobile</t>
         </is>
       </c>
-      <c r="C44" s="6" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>iOS / Android</t>
         </is>
       </c>
-      <c r="D44" s="6" t="inlineStr">
+      <c r="D44" s="4" t="inlineStr">
         <is>
           <t>AR/AP quick view</t>
         </is>
       </c>
-      <c r="E44" s="6" t="inlineStr">
+      <c r="E44" s="4" t="inlineStr">
         <is>
           <t>Customer/supplier search, open items</t>
         </is>
       </c>
-      <c r="F44" s="6" t="inlineStr">
+      <c r="F44" s="4" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="6" t="n">
+      <c r="A45" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B45" s="6" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>WizAccountant Mobile</t>
         </is>
       </c>
-      <c r="C45" s="6" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
         <is>
           <t>iOS / Android</t>
         </is>
       </c>
-      <c r="D45" s="6" t="inlineStr">
+      <c r="D45" s="4" t="inlineStr">
         <is>
           <t>Push notifications</t>
         </is>
       </c>
-      <c r="E45" s="6" t="inlineStr">
+      <c r="E45" s="4" t="inlineStr">
         <is>
           <t>Site offline alert; optional daily summary</t>
         </is>
       </c>
-      <c r="F45" s="6" t="inlineStr">
+      <c r="F45" s="4" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="6" t="n">
+      <c r="A46" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B46" s="6" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>WizAccountant Mobile</t>
         </is>
       </c>
-      <c r="C46" s="6" t="inlineStr">
+      <c r="C46" s="4" t="inlineStr">
         <is>
           <t>iOS / Android</t>
         </is>
       </c>
-      <c r="D46" s="6" t="inlineStr">
+      <c r="D46" s="4" t="inlineStr">
         <is>
           <t>AI chat (read-only)</t>
         </is>
       </c>
-      <c r="E46" s="6" t="inlineStr">
+      <c r="E46" s="4" t="inlineStr">
         <is>
           <t>Same tools as web; mobile UI</t>
         </is>
       </c>
-      <c r="F46" s="6" t="inlineStr">
+      <c r="F46" s="4" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="6" t="n">
+      <c r="A47" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B47" s="6" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>WizAccountant Mobile</t>
         </is>
       </c>
-      <c r="C47" s="6" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>iOS / Android</t>
         </is>
       </c>
-      <c r="D47" s="6" t="inlineStr">
+      <c r="D47" s="4" t="inlineStr">
         <is>
           <t>Deep links</t>
         </is>
       </c>
-      <c r="E47" s="6" t="inlineStr">
+      <c r="E47" s="4" t="inlineStr">
         <is>
           <t>Open entity from notification</t>
         </is>
       </c>
-      <c r="F47" s="6" t="inlineStr">
+      <c r="F47" s="4" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="7" t="n">
+      <c r="A48" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B48" s="7" t="inlineStr">
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C48" s="7" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D48" s="7" t="inlineStr">
+      <c r="D48" s="5" t="inlineStr">
         <is>
           <t>Idempotency store</t>
         </is>
       </c>
-      <c r="E48" s="7" t="inlineStr">
+      <c r="E48" s="5" t="inlineStr">
         <is>
           <t>Local SQLite: idempotencyKey → result hash</t>
         </is>
       </c>
-      <c r="F48" s="7" t="inlineStr">
+      <c r="F48" s="5" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="7" t="n">
+      <c r="A49" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B49" s="7" t="inlineStr">
+      <c r="B49" s="5" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C49" s="7" t="inlineStr">
+      <c r="C49" s="5" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D49" s="7" t="inlineStr">
+      <c r="D49" s="5" t="inlineStr">
         <is>
           <t>Write handlers</t>
         </is>
       </c>
-      <c r="E49" s="7" t="inlineStr">
+      <c r="E49" s="5" t="inlineStr">
         <is>
           <t>Allowlisted post operations</t>
         </is>
       </c>
-      <c r="F49" s="7" t="inlineStr">
+      <c r="F49" s="5" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="7" t="n">
+      <c r="A50" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B50" s="7" t="inlineStr">
+      <c r="B50" s="5" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C50" s="7" t="inlineStr">
+      <c r="C50" s="5" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D50" s="7" t="inlineStr">
+      <c r="D50" s="5" t="inlineStr">
         <is>
           <t>Transactions</t>
         </is>
       </c>
-      <c r="E50" s="7" t="inlineStr">
+      <c r="E50" s="5" t="inlineStr">
         <is>
           <t>BeginTran / Commit / Rollback per action</t>
         </is>
       </c>
-      <c r="F50" s="7" t="inlineStr">
+      <c r="F50" s="5" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="7" t="n">
+      <c r="A51" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B51" s="7" t="inlineStr">
+      <c r="B51" s="5" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C51" s="7" t="inlineStr">
+      <c r="C51" s="5" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D51" s="7" t="inlineStr">
+      <c r="D51" s="5" t="inlineStr">
         <is>
           <t>StartNewBatch</t>
         </is>
       </c>
-      <c r="E51" s="7" t="inlineStr">
+      <c r="E51" s="5" t="inlineStr">
         <is>
           <t>Separate audit batches per post</t>
         </is>
       </c>
-      <c r="F51" s="7" t="inlineStr">
+      <c r="F51" s="5" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="7" t="n">
+      <c r="A52" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B52" s="7" t="inlineStr">
+      <c r="B52" s="5" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C52" s="7" t="inlineStr">
+      <c r="C52" s="5" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D52" s="7" t="inlineStr">
+      <c r="D52" s="5" t="inlineStr">
         <is>
           <t>Error mapping</t>
         </is>
       </c>
-      <c r="E52" s="7" t="inlineStr">
+      <c r="E52" s="5" t="inlineStr">
         <is>
           <t>Evolution exceptions → stable error codes</t>
         </is>
       </c>
-      <c r="F52" s="7" t="inlineStr">
+      <c r="F52" s="5" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="7" t="n">
+      <c r="A53" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B53" s="7" t="inlineStr">
+      <c r="B53" s="5" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C53" s="7" t="inlineStr">
+      <c r="C53" s="5" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D53" s="7" t="inlineStr">
+      <c r="D53" s="5" t="inlineStr">
         <is>
           <t>Consent (optional)</t>
         </is>
       </c>
-      <c r="E53" s="7" t="inlineStr">
+      <c r="E53" s="5" t="inlineStr">
         <is>
           <t>Tray: Allow cloud to post for 1 hour</t>
         </is>
       </c>
-      <c r="F53" s="7" t="inlineStr">
+      <c r="F53" s="5" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="7" t="n">
+      <c r="A54" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B54" s="7" t="inlineStr">
+      <c r="B54" s="5" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C54" s="7" t="inlineStr">
+      <c r="C54" s="5" t="inlineStr">
         <is>
           <t>Sage SDK</t>
         </is>
       </c>
-      <c r="D54" s="7" t="inlineStr">
+      <c r="D54" s="5" t="inlineStr">
         <is>
           <t>GL</t>
         </is>
       </c>
-      <c r="E54" s="7" t="inlineStr">
+      <c r="E54" s="5" t="inlineStr">
         <is>
           <t>GLTransaction.Post; journal batch create only — VAT legs per SDK</t>
         </is>
       </c>
-      <c r="F54" s="7" t="inlineStr">
+      <c r="F54" s="5" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="7" t="n">
+      <c r="A55" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B55" s="7" t="inlineStr">
+      <c r="B55" s="5" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C55" s="7" t="inlineStr">
+      <c r="C55" s="5" t="inlineStr">
         <is>
           <t>Sage SDK</t>
         </is>
       </c>
-      <c r="D55" s="7" t="inlineStr">
+      <c r="D55" s="5" t="inlineStr">
         <is>
           <t>AR</t>
         </is>
       </c>
-      <c r="E55" s="7" t="inlineStr">
+      <c r="E55" s="5" t="inlineStr">
         <is>
           <t>CustomerTransaction.Post; Allocations.Save — Codes per site config</t>
         </is>
       </c>
-      <c r="F55" s="7" t="inlineStr">
+      <c r="F55" s="5" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="7" t="n">
+      <c r="A56" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B56" s="7" t="inlineStr">
+      <c r="B56" s="5" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C56" s="7" t="inlineStr">
+      <c r="C56" s="5" t="inlineStr">
         <is>
           <t>Sage SDK</t>
         </is>
       </c>
-      <c r="D56" s="7" t="inlineStr">
+      <c r="D56" s="5" t="inlineStr">
         <is>
           <t>AP</t>
         </is>
       </c>
-      <c r="E56" s="7" t="inlineStr">
+      <c r="E56" s="5" t="inlineStr">
         <is>
           <t>SupplierTransaction.Post; Allocations.Save — Codes per site config</t>
         </is>
       </c>
-      <c r="F56" s="7" t="inlineStr">
+      <c r="F56" s="5" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="7" t="n">
+      <c r="A57" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B57" s="7" t="inlineStr">
+      <c r="B57" s="5" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C57" s="7" t="inlineStr">
+      <c r="C57" s="5" t="inlineStr">
         <is>
           <t>Sage SDK</t>
         </is>
       </c>
-      <c r="D57" s="7" t="inlineStr">
+      <c r="D57" s="5" t="inlineStr">
         <is>
           <t>Master (limited)</t>
         </is>
       </c>
-      <c r="E57" s="7" t="inlineStr">
+      <c r="E57" s="5" t="inlineStr">
         <is>
           <t>Customer.Save, Supplier.Save — Role-gated</t>
         </is>
       </c>
-      <c r="F57" s="7" t="inlineStr">
+      <c r="F57" s="5" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="7" t="n">
+      <c r="A58" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B58" s="7" t="inlineStr">
+      <c r="B58" s="5" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C58" s="7" t="inlineStr">
+      <c r="C58" s="5" t="inlineStr">
         <is>
           <t>Sage SDK</t>
         </is>
       </c>
-      <c r="D58" s="7" t="inlineStr">
+      <c r="D58" s="5" t="inlineStr">
         <is>
           <t>Orders (optional 3b)</t>
         </is>
       </c>
-      <c r="E58" s="7" t="inlineStr">
+      <c r="E58" s="5" t="inlineStr">
         <is>
           <t>SalesOrder/PurchaseOrder Save + Process partial — Sub-phase</t>
         </is>
       </c>
-      <c r="F58" s="7" t="inlineStr">
+      <c r="F58" s="5" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="7" t="n">
+      <c r="A59" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B59" s="7" t="inlineStr">
+      <c r="B59" s="5" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C59" s="7" t="inlineStr">
+      <c r="C59" s="5" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D59" s="7" t="inlineStr">
+      <c r="D59" s="5" t="inlineStr">
         <is>
           <t>Approval queue</t>
         </is>
       </c>
-      <c r="E59" s="7" t="inlineStr">
+      <c r="E59" s="5" t="inlineStr">
         <is>
           <t>Proposed journal/payment → approver → execute</t>
         </is>
       </c>
-      <c r="F59" s="7" t="inlineStr">
+      <c r="F59" s="5" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="7" t="n">
+      <c r="A60" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B60" s="7" t="inlineStr">
+      <c r="B60" s="5" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C60" s="7" t="inlineStr">
+      <c r="C60" s="5" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D60" s="7" t="inlineStr">
+      <c r="D60" s="5" t="inlineStr">
         <is>
           <t>Maker-checker</t>
         </is>
       </c>
-      <c r="E60" s="7" t="inlineStr">
+      <c r="E60" s="5" t="inlineStr">
         <is>
           <t>Prepare vs approve roles</t>
         </is>
       </c>
-      <c r="F60" s="7" t="inlineStr">
+      <c r="F60" s="5" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="7" t="n">
+      <c r="A61" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B61" s="7" t="inlineStr">
+      <c r="B61" s="5" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C61" s="7" t="inlineStr">
+      <c r="C61" s="5" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D61" s="7" t="inlineStr">
+      <c r="D61" s="5" t="inlineStr">
         <is>
           <t>AI propose, human approve</t>
         </is>
       </c>
-      <c r="E61" s="7" t="inlineStr">
+      <c r="E61" s="5" t="inlineStr">
         <is>
           <t>Draft only until approved</t>
         </is>
       </c>
-      <c r="F61" s="7" t="inlineStr">
+      <c r="F61" s="5" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="7" t="n">
+      <c r="A62" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B62" s="7" t="inlineStr">
+      <c r="B62" s="5" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C62" s="7" t="inlineStr">
+      <c r="C62" s="5" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D62" s="7" t="inlineStr">
+      <c r="D62" s="5" t="inlineStr">
         <is>
           <t>Write audit</t>
         </is>
       </c>
-      <c r="E62" s="7" t="inlineStr">
+      <c r="E62" s="5" t="inlineStr">
         <is>
           <t>Before/after, user, approver, Evolution ref</t>
         </is>
       </c>
-      <c r="F62" s="7" t="inlineStr">
+      <c r="F62" s="5" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="7" t="n">
+      <c r="A63" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B63" s="7" t="inlineStr">
+      <c r="B63" s="5" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C63" s="7" t="inlineStr">
+      <c r="C63" s="5" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D63" s="7" t="inlineStr">
+      <c r="D63" s="5" t="inlineStr">
         <is>
           <t>Workflows (starter)</t>
         </is>
       </c>
-      <c r="E63" s="7" t="inlineStr">
+      <c r="E63" s="5" t="inlineStr">
         <is>
           <t>Month-end checklist, payment run proposal</t>
         </is>
       </c>
-      <c r="F63" s="7" t="inlineStr">
+      <c r="F63" s="5" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="7" t="n">
+      <c r="A64" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B64" s="7" t="inlineStr">
+      <c r="B64" s="5" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C64" s="7" t="inlineStr">
+      <c r="C64" s="5" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D64" s="7" t="inlineStr">
+      <c r="D64" s="5" t="inlineStr">
         <is>
           <t>Site config sync</t>
         </is>
       </c>
-      <c r="E64" s="7" t="inlineStr">
+      <c r="E64" s="5" t="inlineStr">
         <is>
           <t>Transaction codes, tax, branch</t>
         </is>
       </c>
-      <c r="F64" s="7" t="inlineStr">
+      <c r="F64" s="5" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="7" t="n">
+      <c r="A65" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B65" s="7" t="inlineStr">
+      <c r="B65" s="5" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C65" s="7" t="inlineStr">
+      <c r="C65" s="5" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D65" s="7" t="inlineStr">
+      <c r="D65" s="5" t="inlineStr">
         <is>
           <t>Rollback messaging</t>
         </is>
       </c>
-      <c r="E65" s="7" t="inlineStr">
+      <c r="E65" s="5" t="inlineStr">
         <is>
           <t>Posts not auto-reversed in product</t>
         </is>
       </c>
-      <c r="F65" s="7" t="inlineStr">
+      <c r="F65" s="5" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="7" t="n">
+      <c r="A66" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B66" s="7" t="inlineStr">
+      <c r="B66" s="5" t="inlineStr">
         <is>
           <t>WizAccountant Mobile</t>
         </is>
       </c>
-      <c r="C66" s="7" t="inlineStr">
+      <c r="C66" s="5" t="inlineStr">
         <is>
           <t>iOS / Android</t>
         </is>
       </c>
-      <c r="D66" s="7" t="inlineStr">
+      <c r="D66" s="5" t="inlineStr">
         <is>
           <t>Approval inbox</t>
         </is>
       </c>
-      <c r="E66" s="7" t="inlineStr">
+      <c r="E66" s="5" t="inlineStr">
         <is>
           <t>Pending journals, payments, allocations</t>
         </is>
       </c>
-      <c r="F66" s="7" t="inlineStr">
+      <c r="F66" s="5" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="7" t="n">
+      <c r="A67" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B67" s="7" t="inlineStr">
+      <c r="B67" s="5" t="inlineStr">
         <is>
           <t>WizAccountant Mobile</t>
         </is>
       </c>
-      <c r="C67" s="7" t="inlineStr">
+      <c r="C67" s="5" t="inlineStr">
         <is>
           <t>iOS / Android</t>
         </is>
       </c>
-      <c r="D67" s="7" t="inlineStr">
+      <c r="D67" s="5" t="inlineStr">
         <is>
           <t>Approve / reject</t>
         </is>
       </c>
-      <c r="E67" s="7" t="inlineStr">
+      <c r="E67" s="5" t="inlineStr">
         <is>
           <t>Maker-checker with comment</t>
         </is>
       </c>
-      <c r="F67" s="7" t="inlineStr">
+      <c r="F67" s="5" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="7" t="n">
+      <c r="A68" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B68" s="7" t="inlineStr">
+      <c r="B68" s="5" t="inlineStr">
         <is>
           <t>WizAccountant Mobile</t>
         </is>
       </c>
-      <c r="C68" s="7" t="inlineStr">
+      <c r="C68" s="5" t="inlineStr">
         <is>
           <t>iOS / Android</t>
         </is>
       </c>
-      <c r="D68" s="7" t="inlineStr">
+      <c r="D68" s="5" t="inlineStr">
         <is>
           <t>Push notifications</t>
         </is>
       </c>
-      <c r="E68" s="7" t="inlineStr">
+      <c r="E68" s="5" t="inlineStr">
         <is>
           <t>Approval required + deep link</t>
         </is>
       </c>
-      <c r="F68" s="7" t="inlineStr">
+      <c r="F68" s="5" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="7" t="n">
+      <c r="A69" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B69" s="7" t="inlineStr">
+      <c r="B69" s="5" t="inlineStr">
         <is>
           <t>WizAccountant Mobile</t>
         </is>
       </c>
-      <c r="C69" s="7" t="inlineStr">
+      <c r="C69" s="5" t="inlineStr">
         <is>
           <t>iOS / Android</t>
         </is>
       </c>
-      <c r="D69" s="7" t="inlineStr">
+      <c r="D69" s="5" t="inlineStr">
         <is>
           <t>AI drafts</t>
         </is>
       </c>
-      <c r="E69" s="7" t="inlineStr">
+      <c r="E69" s="5" t="inlineStr">
         <is>
           <t>View proposal; approve via flow</t>
         </is>
       </c>
-      <c r="F69" s="7" t="inlineStr">
+      <c r="F69" s="5" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="7" t="n">
+      <c r="A70" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B70" s="7" t="inlineStr">
+      <c r="B70" s="5" t="inlineStr">
         <is>
           <t>WizAccountant Mobile</t>
         </is>
       </c>
-      <c r="C70" s="7" t="inlineStr">
+      <c r="C70" s="5" t="inlineStr">
         <is>
           <t>iOS / Android</t>
         </is>
       </c>
-      <c r="D70" s="7" t="inlineStr">
+      <c r="D70" s="5" t="inlineStr">
         <is>
           <t>Audit (read)</t>
         </is>
       </c>
-      <c r="E70" s="7" t="inlineStr">
+      <c r="E70" s="5" t="inlineStr">
         <is>
           <t>Approval history per item</t>
         </is>
       </c>
-      <c r="F70" s="7" t="inlineStr">
+      <c r="F70" s="5" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="8" t="n">
+      <c r="A71" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B71" s="8" t="inlineStr">
+      <c r="B71" s="6" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C71" s="8" t="inlineStr">
+      <c r="C71" s="6" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D71" s="8" t="inlineStr">
+      <c r="D71" s="6" t="inlineStr">
         <is>
           <t>Multi-company</t>
         </is>
       </c>
-      <c r="E71" s="8" t="inlineStr">
+      <c r="E71" s="6" t="inlineStr">
         <is>
           <t>One agent → multiple company DBs</t>
         </is>
       </c>
-      <c r="F71" s="8" t="inlineStr">
+      <c r="F71" s="6" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="8" t="n">
+      <c r="A72" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B72" s="8" t="inlineStr">
+      <c r="B72" s="6" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C72" s="8" t="inlineStr">
+      <c r="C72" s="6" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D72" s="8" t="inlineStr">
+      <c r="D72" s="6" t="inlineStr">
         <is>
           <t>Branch context</t>
         </is>
       </c>
-      <c r="E72" s="8" t="inlineStr">
+      <c r="E72" s="6" t="inlineStr">
         <is>
           <t>SetBranchContext per site</t>
         </is>
       </c>
-      <c r="F72" s="8" t="inlineStr">
+      <c r="F72" s="6" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="8" t="n">
+      <c r="A73" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B73" s="8" t="inlineStr">
+      <c r="B73" s="6" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C73" s="8" t="inlineStr">
+      <c r="C73" s="6" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D73" s="8" t="inlineStr">
+      <c r="D73" s="6" t="inlineStr">
         <is>
           <t>Heavy modules</t>
         </is>
       </c>
-      <c r="E73" s="8" t="inlineStr">
+      <c r="E73" s="6" t="inlineStr">
         <is>
           <t>CN, RTS, inventory adj, warehouse transfer</t>
         </is>
       </c>
-      <c r="F73" s="8" t="inlineStr">
+      <c r="F73" s="6" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="8" t="n">
+      <c r="A74" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B74" s="8" t="inlineStr">
+      <c r="B74" s="6" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C74" s="8" t="inlineStr">
+      <c r="C74" s="6" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D74" s="8" t="inlineStr">
+      <c r="D74" s="6" t="inlineStr">
         <is>
           <t>Order processing</t>
         </is>
       </c>
-      <c r="E74" s="8" t="inlineStr">
+      <c r="E74" s="6" t="inlineStr">
         <is>
           <t>SO/PO Process, partial, Complete</t>
         </is>
       </c>
-      <c r="F74" s="8" t="inlineStr">
+      <c r="F74" s="6" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="8" t="n">
+      <c r="A75" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B75" s="8" t="inlineStr">
+      <c r="B75" s="6" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C75" s="8" t="inlineStr">
+      <c r="C75" s="6" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D75" s="8" t="inlineStr">
+      <c r="D75" s="6" t="inlineStr">
         <is>
           <t>Offline queue (optional)</t>
         </is>
       </c>
-      <c r="E75" s="8" t="inlineStr">
+      <c r="E75" s="6" t="inlineStr">
         <is>
           <t>Buffer approved jobs when Sage busy</t>
         </is>
       </c>
-      <c r="F75" s="8" t="inlineStr">
+      <c r="F75" s="6" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="8" t="n">
+      <c r="A76" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B76" s="8" t="inlineStr">
+      <c r="B76" s="6" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C76" s="8" t="inlineStr">
+      <c r="C76" s="6" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D76" s="8" t="inlineStr">
+      <c r="D76" s="6" t="inlineStr">
         <is>
           <t>Practice mode</t>
         </is>
       </c>
-      <c r="E76" s="8" t="inlineStr">
+      <c r="E76" s="6" t="inlineStr">
         <is>
           <t>One firm, many client sites</t>
         </is>
       </c>
-      <c r="F76" s="8" t="inlineStr">
+      <c r="F76" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="8" t="n">
+      <c r="A77" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B77" s="8" t="inlineStr">
+      <c r="B77" s="6" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C77" s="8" t="inlineStr">
+      <c r="C77" s="6" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D77" s="8" t="inlineStr">
+      <c r="D77" s="6" t="inlineStr">
         <is>
           <t>RBAC</t>
         </is>
       </c>
-      <c r="E77" s="8" t="inlineStr">
+      <c r="E77" s="6" t="inlineStr">
         <is>
           <t>Read vs propose vs approve vs admin</t>
         </is>
       </c>
-      <c r="F77" s="8" t="inlineStr">
+      <c r="F77" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="8" t="n">
+      <c r="A78" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B78" s="8" t="inlineStr">
+      <c r="B78" s="6" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C78" s="8" t="inlineStr">
+      <c r="C78" s="6" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D78" s="8" t="inlineStr">
+      <c r="D78" s="6" t="inlineStr">
         <is>
           <t>SSO</t>
         </is>
       </c>
-      <c r="E78" s="8" t="inlineStr">
+      <c r="E78" s="6" t="inlineStr">
         <is>
           <t>Azure AD / Google</t>
         </is>
       </c>
-      <c r="F78" s="8" t="inlineStr">
+      <c r="F78" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="8" t="n">
+      <c r="A79" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B79" s="8" t="inlineStr">
+      <c r="B79" s="6" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C79" s="8" t="inlineStr">
+      <c r="C79" s="6" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D79" s="8" t="inlineStr">
+      <c r="D79" s="6" t="inlineStr">
         <is>
           <t>Monitoring</t>
         </is>
       </c>
-      <c r="E79" s="8" t="inlineStr">
+      <c r="E79" s="6" t="inlineStr">
         <is>
           <t>Site SLA, failed job alerts</t>
         </is>
       </c>
-      <c r="F79" s="8" t="inlineStr">
+      <c r="F79" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="8" t="n">
+      <c r="A80" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B80" s="8" t="inlineStr">
+      <c r="B80" s="6" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C80" s="8" t="inlineStr">
+      <c r="C80" s="6" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D80" s="8" t="inlineStr">
+      <c r="D80" s="6" t="inlineStr">
         <is>
           <t>Billing</t>
         </is>
       </c>
-      <c r="E80" s="8" t="inlineStr">
+      <c r="E80" s="6" t="inlineStr">
         <is>
           <t>Per site / per user hooks</t>
         </is>
       </c>
-      <c r="F80" s="8" t="inlineStr">
+      <c r="F80" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="8" t="n">
+      <c r="A81" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B81" s="8" t="inlineStr">
+      <c r="B81" s="6" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C81" s="8" t="inlineStr">
+      <c r="C81" s="6" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D81" s="8" t="inlineStr">
+      <c r="D81" s="6" t="inlineStr">
         <is>
           <t>Compliance</t>
         </is>
       </c>
-      <c r="E81" s="8" t="inlineStr">
+      <c r="E81" s="6" t="inlineStr">
         <is>
           <t>DPA templates, retention</t>
         </is>
       </c>
-      <c r="F81" s="8" t="inlineStr">
+      <c r="F81" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="8" t="n">
+      <c r="A82" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B82" s="8" t="inlineStr">
+      <c r="B82" s="6" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C82" s="8" t="inlineStr">
+      <c r="C82" s="6" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D82" s="8" t="inlineStr">
+      <c r="D82" s="6" t="inlineStr">
         <is>
           <t>Advanced AI</t>
         </is>
       </c>
-      <c r="E82" s="8" t="inlineStr">
+      <c r="E82" s="6" t="inlineStr">
         <is>
           <t>Multi-step workflows; doc upload draft</t>
         </is>
       </c>
-      <c r="F82" s="8" t="inlineStr">
+      <c r="F82" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="8" t="n">
+      <c r="A83" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B83" s="8" t="inlineStr">
+      <c r="B83" s="6" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C83" s="8" t="inlineStr">
+      <c r="C83" s="6" t="inlineStr">
         <is>
           <t>Sage SDK</t>
         </is>
       </c>
-      <c r="D83" s="8" t="inlineStr">
+      <c r="D83" s="6" t="inlineStr">
         <is>
           <t>Inventory</t>
         </is>
       </c>
-      <c r="E83" s="8" t="inlineStr">
+      <c r="E83" s="6" t="inlineStr">
         <is>
           <t>InventoryTransaction.Post; CN/RTS Process; warehouse</t>
         </is>
       </c>
-      <c r="F83" s="8" t="inlineStr">
+      <c r="F83" s="6" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="8" t="n">
+      <c r="A84" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B84" s="8" t="inlineStr">
+      <c r="B84" s="6" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C84" s="8" t="inlineStr">
+      <c r="C84" s="6" t="inlineStr">
         <is>
           <t>Sage SDK</t>
         </is>
       </c>
-      <c r="D84" s="8" t="inlineStr">
+      <c r="D84" s="6" t="inlineStr">
         <is>
           <t>Orders</t>
         </is>
       </c>
-      <c r="E84" s="8" t="inlineStr">
+      <c r="E84" s="6" t="inlineStr">
         <is>
           <t>Full SO/PO lifecycle</t>
         </is>
       </c>
-      <c r="F84" s="8" t="inlineStr">
+      <c r="F84" s="6" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="8" t="n">
+      <c r="A85" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B85" s="8" t="inlineStr">
+      <c r="B85" s="6" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C85" s="8" t="inlineStr">
+      <c r="C85" s="6" t="inlineStr">
         <is>
           <t>Sage SDK</t>
         </is>
       </c>
-      <c r="D85" s="8" t="inlineStr">
+      <c r="D85" s="6" t="inlineStr">
         <is>
           <t>CRM</t>
         </is>
       </c>
-      <c r="E85" s="8" t="inlineStr">
+      <c r="E85" s="6" t="inlineStr">
         <is>
           <t>Incidents (if needed)</t>
         </is>
       </c>
-      <c r="F85" s="8" t="inlineStr">
+      <c r="F85" s="6" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="8" t="n">
+      <c r="A86" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B86" s="8" t="inlineStr">
+      <c r="B86" s="6" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C86" s="8" t="inlineStr">
+      <c r="C86" s="6" t="inlineStr">
         <is>
           <t>Sage SDK</t>
         </is>
       </c>
-      <c r="D86" s="8" t="inlineStr">
+      <c r="D86" s="6" t="inlineStr">
         <is>
           <t>Job costing</t>
         </is>
       </c>
-      <c r="E86" s="8" t="inlineStr">
+      <c r="E86" s="6" t="inlineStr">
         <is>
           <t>Job card Save only (no process)</t>
         </is>
       </c>
-      <c r="F86" s="8" t="inlineStr">
+      <c r="F86" s="6" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="8" t="n">
+      <c r="A87" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B87" s="8" t="inlineStr">
+      <c r="B87" s="6" t="inlineStr">
         <is>
           <t>WizAccountant Mobile</t>
         </is>
       </c>
-      <c r="C87" s="8" t="inlineStr">
+      <c r="C87" s="6" t="inlineStr">
         <is>
           <t>iOS / Android</t>
         </is>
       </c>
-      <c r="D87" s="8" t="inlineStr">
+      <c r="D87" s="6" t="inlineStr">
         <is>
           <t>Practice mode</t>
         </is>
       </c>
-      <c r="E87" s="8" t="inlineStr">
+      <c r="E87" s="6" t="inlineStr">
         <is>
           <t>Switch client site for accounting firms</t>
         </is>
       </c>
-      <c r="F87" s="8" t="inlineStr">
+      <c r="F87" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="8" t="n">
+      <c r="A88" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B88" s="8" t="inlineStr">
+      <c r="B88" s="6" t="inlineStr">
         <is>
           <t>WizAccountant Mobile</t>
         </is>
       </c>
-      <c r="C88" s="8" t="inlineStr">
+      <c r="C88" s="6" t="inlineStr">
         <is>
           <t>iOS / Android</t>
         </is>
       </c>
-      <c r="D88" s="8" t="inlineStr">
+      <c r="D88" s="6" t="inlineStr">
         <is>
           <t>Inventory (read)</t>
         </is>
       </c>
-      <c r="E88" s="8" t="inlineStr">
+      <c r="E88" s="6" t="inlineStr">
         <is>
           <t>Stock lookup, low-stock push alert</t>
         </is>
       </c>
-      <c r="F88" s="8" t="inlineStr">
+      <c r="F88" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="8" t="n">
+      <c r="A89" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B89" s="8" t="inlineStr">
+      <c r="B89" s="6" t="inlineStr">
         <is>
           <t>WizAccountant Mobile</t>
         </is>
       </c>
-      <c r="C89" s="8" t="inlineStr">
+      <c r="C89" s="6" t="inlineStr">
         <is>
           <t>iOS / Android</t>
         </is>
       </c>
-      <c r="D89" s="8" t="inlineStr">
+      <c r="D89" s="6" t="inlineStr">
         <is>
           <t>Workflows</t>
         </is>
       </c>
-      <c r="E89" s="8" t="inlineStr">
+      <c r="E89" s="6" t="inlineStr">
         <is>
           <t>Starter checklist steps from phone</t>
         </is>
       </c>
-      <c r="F89" s="8" t="inlineStr">
+      <c r="F89" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="8" t="n">
+      <c r="A90" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B90" s="8" t="inlineStr">
+      <c r="B90" s="6" t="inlineStr">
         <is>
           <t>WizAccountant Mobile</t>
         </is>
       </c>
-      <c r="C90" s="8" t="inlineStr">
+      <c r="C90" s="6" t="inlineStr">
         <is>
           <t>iOS / Android</t>
         </is>
       </c>
-      <c r="D90" s="8" t="inlineStr">
+      <c r="D90" s="6" t="inlineStr">
         <is>
           <t>Tablet layout</t>
         </is>
       </c>
-      <c r="E90" s="8" t="inlineStr">
+      <c r="E90" s="6" t="inlineStr">
         <is>
           <t>iPad / Android tablet for approvers</t>
         </is>
       </c>
-      <c r="F90" s="8" t="inlineStr">
+      <c r="F90" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="8" t="n">
+      <c r="A91" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B91" s="8" t="inlineStr">
+      <c r="B91" s="6" t="inlineStr">
         <is>
           <t>WizAccountant Mobile</t>
         </is>
       </c>
-      <c r="C91" s="8" t="inlineStr">
+      <c r="C91" s="6" t="inlineStr">
         <is>
           <t>iOS / Android</t>
         </is>
       </c>
-      <c r="D91" s="8" t="inlineStr">
+      <c r="D91" s="6" t="inlineStr">
         <is>
           <t>App store release</t>
         </is>
       </c>
-      <c r="E91" s="8" t="inlineStr">
+      <c r="E91" s="6" t="inlineStr">
         <is>
           <t>Production signing, crash analytics, staged rollout</t>
         </is>
       </c>
-      <c r="F91" s="8" t="inlineStr">
+      <c r="F91" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="5" t="n">
+      <c r="A92" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B92" s="5" t="inlineStr">
+      <c r="B92" s="3" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C92" s="5" t="inlineStr">
+      <c r="C92" s="3" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D92" s="5" t="inlineStr">
+      <c r="D92" s="3" t="inlineStr">
         <is>
           <t>API mobile-ready</t>
         </is>
       </c>
-      <c r="E92" s="5" t="inlineStr">
+      <c r="E92" s="3" t="inlineStr">
         <is>
           <t>JWT, same job endpoints — no native app in P1</t>
         </is>
       </c>
-      <c r="F92" s="5" t="inlineStr">
+      <c r="F92" s="3" t="inlineStr">
         <is>
           <t>Read</t>
         </is>

--- a/WizAccountant.xlsx
+++ b/WizAccountant.xlsx
@@ -9,16 +9,18 @@
   <sheets>
     <sheet name="Overview" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Phase 1 Checklist" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Phase Summary" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Features" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Success Criteria" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Platform (Cross-Phase)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Mobile Strategy" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Sage Module Priority" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Not Building (Plan 1)" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Phase 1 Exclusions" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="SDK Limits (Phase 3+)" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Execution Status" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Phase 2 Checklist" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Phase 3 Checklist" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Phase Summary" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Features" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Success Criteria" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Platform (Cross-Phase)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Mobile Strategy" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Sage Module Priority" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Not Building (Plan 1)" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Phase 1 Exclusions" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="SDK Limits (Phase 3+)" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Execution Status" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -42,7 +44,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -57,6 +59,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -92,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -102,6 +114,8 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -625,6 +639,228 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Phases</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>GL</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1–3</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Accounts, journals</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>AR / AP</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1–3</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Masters, transactions, allocations</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2 read, 4 write</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Items, adjustments</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Sales / Purchase orders</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>3b / 4</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>High complexity</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CRM / Job costing</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>4+</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Niche; job card no process via SDK</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="49" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>WizVPN / network tunnel to LAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Hosted customer DB restore as primary product</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Full cloud replacement of Evolution UI (Plan 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Raw SQL access from web or AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Evolution report printing via SDK</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Unrestricted SDK passthrough</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Cashbook / journal batch process via SDK</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Job card process/complete via SDK</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -699,7 +935,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -765,7 +1001,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2343,6 +2579,896 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="72" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>P2-01</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Expanded SDK reads (GL tx, orders, inventory, master data)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>P2-02</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>AR/AP open items handlers</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>P2-03</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Criteria builder (date, account, reference) + pagination</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>P2-04</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>site.diagnostics support bundle</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>P2-05</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>dashboard.summary + search.global</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>P2-06</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Insight dashboard + search endpoints</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>P2-07</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Read-only AI chat + conversation history</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>P2-08</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>CSV export from job results</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>P2-09</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Notification email stub + log</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>P2-10</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Per-site rate limiting</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>P2-11</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>API versioning /api/v1/insight/tools</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>P2-12</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Insight UI — dashboard, AR/AP, search, chat</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>P2-13</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>PHASE2-AI-GUARDRAILS.md</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>P2-14</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Native iOS/Android app (Expo — mobile/wiz-accountant)</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>P2-15</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Cloud</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Production JWT + Brevo email integration</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>NEXT</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>P2-16</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Signed auto-update channel</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>14 / 16 complete</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="72" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>P3-01</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Idempotency store (SQLite)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>P3-02</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Write handlers GL/AR/AP + master save</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>P3-03</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Sage transactions BeginTran/Commit + error mapping</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>P3-04</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Write consent store (Tray-ready)</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>P3-05</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Approval queue propose/approve/reject</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>P3-06</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Maker-checker roles (Preparer vs Approver)</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>P3-07</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>AI propose draft (structured JSON)</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>P3-08</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Write audit before/after + Evolution ref</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>P3-09</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Workflow templates + site config sync</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>P3-10</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Act UI — inbox, propose, audit</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>P3-11</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>PHASE3-APPROVALS.md + rollback messaging</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>P3-12</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Approval inbox native app (Approvals tab)</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>P3-13</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Tray consent menu item</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>13 / 13 complete</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2563,7 +3689,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2613,2730 +3739,2730 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>Windows Service</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>Auto-start, recovery, structured logging</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>System tray app</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Pairing wizard, connection status, device/site ID, open logs</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Pairing</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>One-time code from cloud → store siteId + credentials (DPAPI)</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Cloud link</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Outbound TLS; WebSocket/SignalR + REST fallback long-poll</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>Heartbeat</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Every 30–60s; version, SDK/Evolution version, company DB name</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Local config</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Evolution connection profile, SDK agent user (encrypted)</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Health handler</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>Site.Health — DB reachable, SDK auth OK</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>Sage SDK</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>GL</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>GLAccount.List, GLAccount.Get</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>Sage SDK</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>AR</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>Customer.List, Customer.Get, CustomerTransaction.List</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>Sage SDK</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>AP</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>Supplier.List, Supplier.Get, SupplierTransaction.List</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>Sage SDK</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>Reports</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>Trial balance–style extracts (scoped queries)</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>Sage SDK</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>Inventory (optional)</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>InventoryItem.List, InventoryItem.Get</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>Auth</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>Email/password or SSO stub; tenants + users</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>Sites</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>Register tenant → pairing code → list sites, last seen</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>Connector Hub</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>Route jobs to siteId; job queue + timeout</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>Admin UI</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>Sites list, connection status, Test connection</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>Job API</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>Submit job → wait/poll result (sync read 30–60s cap)</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>Audit (basic)</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>Log job type, user, site, timestamp, success/fail</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="n">
+      <c r="A20" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>Expanded reads</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E20" s="6" t="inlineStr">
         <is>
           <t>Outstanding balances, aged analysis, detail by Autoidx</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="F20" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="n">
+      <c r="A21" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>Search / filter</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E21" s="6" t="inlineStr">
         <is>
           <t>Criteria builders: account, date range, reference</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F21" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="n">
+      <c r="A22" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
         <is>
           <t>Connection pooling, timeouts, pagination</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="F22" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="n">
+      <c r="A23" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>Diagnostics</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="E23" s="6" t="inlineStr">
         <is>
           <t>Support bundle: redacted logs, versions, last 50 jobs</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr">
+      <c r="F23" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="n">
+      <c r="A24" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t>Auto-update (optional)</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="E24" s="6" t="inlineStr">
         <is>
           <t>Signed installer check channel</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="F24" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="n">
+      <c r="A25" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>Sage SDK</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t>AR</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="E25" s="6" t="inlineStr">
         <is>
           <t>Open items/outstanding; allocations read</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="F25" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="n">
+      <c r="A26" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>Sage SDK</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D26" s="6" t="inlineStr">
         <is>
           <t>AP</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="E26" s="6" t="inlineStr">
         <is>
           <t>Same for suppliers</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="F26" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="n">
+      <c r="A27" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>Sage SDK</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>GL</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="E27" s="6" t="inlineStr">
         <is>
           <t>Transaction list by account/period</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="F27" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="n">
+      <c r="A28" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
         <is>
           <t>Sage SDK</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D28" s="6" t="inlineStr">
         <is>
           <t>Inventory</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="E28" s="6" t="inlineStr">
         <is>
           <t>Stock levels, item search</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="F28" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="n">
+      <c r="A29" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>Sage SDK</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D29" s="6" t="inlineStr">
         <is>
           <t>Orders</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="E29" s="6" t="inlineStr">
         <is>
           <t>SalesOrder.List, PurchaseOrder.List</t>
         </is>
       </c>
-      <c r="F29" s="4" t="inlineStr">
+      <c r="F29" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="n">
+      <c r="A30" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>Sage SDK</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D30" s="6" t="inlineStr">
         <is>
           <t>Master data</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="E30" s="6" t="inlineStr">
         <is>
           <t>Projects, warehouses, tax rates, transaction codes list</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr">
+      <c r="F30" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="n">
+      <c r="A31" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D31" s="6" t="inlineStr">
         <is>
           <t>Dashboard</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="E31" s="6" t="inlineStr">
         <is>
           <t>TB summary, debtors/creditors KPIs</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr">
+      <c r="F31" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="n">
+      <c r="A32" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D32" s="6" t="inlineStr">
         <is>
           <t>AR/AP workspaces</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="E32" s="6" t="inlineStr">
         <is>
           <t>Browse customers/suppliers, drill to transactions</t>
         </is>
       </c>
-      <c r="F32" s="4" t="inlineStr">
+      <c r="F32" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="n">
+      <c r="A33" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D33" s="6" t="inlineStr">
         <is>
           <t>Global search</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="E33" s="6" t="inlineStr">
         <is>
           <t>Cross-entity search</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr">
+      <c r="F33" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="n">
+      <c r="A34" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C34" s="6" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D34" s="6" t="inlineStr">
         <is>
           <t>AI chat (read-only)</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
+      <c r="E34" s="6" t="inlineStr">
         <is>
           <t>Tools = read handlers; citations</t>
         </is>
       </c>
-      <c r="F34" s="4" t="inlineStr">
+      <c r="F34" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="n">
+      <c r="A35" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D35" s="6" t="inlineStr">
         <is>
           <t>Conversation history</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
+      <c r="E35" s="6" t="inlineStr">
         <is>
           <t>Per tenant/user</t>
         </is>
       </c>
-      <c r="F35" s="4" t="inlineStr">
+      <c r="F35" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="n">
+      <c r="A36" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="D36" s="6" t="inlineStr">
         <is>
           <t>Export</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
+      <c r="E36" s="6" t="inlineStr">
         <is>
           <t>CSV/PDF for visible lists</t>
         </is>
       </c>
-      <c r="F36" s="4" t="inlineStr">
+      <c r="F36" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="n">
+      <c r="A37" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="D37" s="6" t="inlineStr">
         <is>
           <t>Notifications</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
+      <c r="E37" s="6" t="inlineStr">
         <is>
           <t>Email: invites, site offline (e.g. Brevo)</t>
         </is>
       </c>
-      <c r="F37" s="4" t="inlineStr">
+      <c r="F37" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="n">
+      <c r="A38" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B38" s="4" t="inlineStr">
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>AI Guardrails</t>
         </is>
       </c>
-      <c r="D38" s="4" t="inlineStr">
+      <c r="D38" s="6" t="inlineStr">
         <is>
           <t>Tool allowlist</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr">
+      <c r="E38" s="6" t="inlineStr">
         <is>
           <t>Read handlers only</t>
         </is>
       </c>
-      <c r="F38" s="4" t="inlineStr">
+      <c r="F38" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="n">
+      <c r="A39" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B39" s="6" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C39" s="6" t="inlineStr">
         <is>
           <t>AI Guardrails</t>
         </is>
       </c>
-      <c r="D39" s="4" t="inlineStr">
+      <c r="D39" s="6" t="inlineStr">
         <is>
           <t>System prompt</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr">
+      <c r="E39" s="6" t="inlineStr">
         <is>
           <t>Never claim posted; suggest approval for actions</t>
         </is>
       </c>
-      <c r="F39" s="4" t="inlineStr">
+      <c r="F39" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="n">
+      <c r="A40" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C40" s="6" t="inlineStr">
         <is>
           <t>AI Guardrails</t>
         </is>
       </c>
-      <c r="D40" s="4" t="inlineStr">
+      <c r="D40" s="6" t="inlineStr">
         <is>
           <t>Data timestamp</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
+      <c r="E40" s="6" t="inlineStr">
         <is>
           <t>Show data as of job completion</t>
         </is>
       </c>
-      <c r="F40" s="4" t="inlineStr">
+      <c r="F40" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="n">
+      <c r="A41" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B41" s="6" t="inlineStr">
         <is>
           <t>WizAccountant Mobile</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C41" s="6" t="inlineStr">
         <is>
           <t>iOS / Android</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="D41" s="6" t="inlineStr">
         <is>
           <t>Auth</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
+      <c r="E41" s="6" t="inlineStr">
         <is>
           <t>Login, biometric unlock, secure token storage</t>
         </is>
       </c>
-      <c r="F41" s="4" t="inlineStr">
+      <c r="F41" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="n">
+      <c r="A42" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B42" s="4" t="inlineStr">
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>WizAccountant Mobile</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="C42" s="6" t="inlineStr">
         <is>
           <t>iOS / Android</t>
         </is>
       </c>
-      <c r="D42" s="4" t="inlineStr">
+      <c r="D42" s="6" t="inlineStr">
         <is>
           <t>Sites</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr">
+      <c r="E42" s="6" t="inlineStr">
         <is>
           <t>List sites, online/offline, switch tenant/site</t>
         </is>
       </c>
-      <c r="F42" s="4" t="inlineStr">
+      <c r="F42" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="n">
+      <c r="A43" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B43" s="6" t="inlineStr">
         <is>
           <t>WizAccountant Mobile</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C43" s="6" t="inlineStr">
         <is>
           <t>iOS / Android</t>
         </is>
       </c>
-      <c r="D43" s="4" t="inlineStr">
+      <c r="D43" s="6" t="inlineStr">
         <is>
           <t>Dashboard</t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr">
+      <c r="E43" s="6" t="inlineStr">
         <is>
           <t>Debtors/creditors totals, TB snapshot (read-only)</t>
         </is>
       </c>
-      <c r="F43" s="4" t="inlineStr">
+      <c r="F43" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="n">
+      <c r="A44" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B44" s="4" t="inlineStr">
+      <c r="B44" s="6" t="inlineStr">
         <is>
           <t>WizAccountant Mobile</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr">
+      <c r="C44" s="6" t="inlineStr">
         <is>
           <t>iOS / Android</t>
         </is>
       </c>
-      <c r="D44" s="4" t="inlineStr">
+      <c r="D44" s="6" t="inlineStr">
         <is>
           <t>AR/AP quick view</t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr">
+      <c r="E44" s="6" t="inlineStr">
         <is>
           <t>Customer/supplier search, open items</t>
         </is>
       </c>
-      <c r="F44" s="4" t="inlineStr">
+      <c r="F44" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="n">
+      <c r="A45" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B45" s="4" t="inlineStr">
+      <c r="B45" s="6" t="inlineStr">
         <is>
           <t>WizAccountant Mobile</t>
         </is>
       </c>
-      <c r="C45" s="4" t="inlineStr">
+      <c r="C45" s="6" t="inlineStr">
         <is>
           <t>iOS / Android</t>
         </is>
       </c>
-      <c r="D45" s="4" t="inlineStr">
+      <c r="D45" s="6" t="inlineStr">
         <is>
           <t>Push notifications</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr">
+      <c r="E45" s="6" t="inlineStr">
         <is>
           <t>Site offline alert; optional daily summary</t>
         </is>
       </c>
-      <c r="F45" s="4" t="inlineStr">
+      <c r="F45" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="n">
+      <c r="A46" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B46" s="4" t="inlineStr">
+      <c r="B46" s="6" t="inlineStr">
         <is>
           <t>WizAccountant Mobile</t>
         </is>
       </c>
-      <c r="C46" s="4" t="inlineStr">
+      <c r="C46" s="6" t="inlineStr">
         <is>
           <t>iOS / Android</t>
         </is>
       </c>
-      <c r="D46" s="4" t="inlineStr">
+      <c r="D46" s="6" t="inlineStr">
         <is>
           <t>AI chat (read-only)</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr">
+      <c r="E46" s="6" t="inlineStr">
         <is>
           <t>Same tools as web; mobile UI</t>
         </is>
       </c>
-      <c r="F46" s="4" t="inlineStr">
+      <c r="F46" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="n">
+      <c r="A47" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B47" s="4" t="inlineStr">
+      <c r="B47" s="6" t="inlineStr">
         <is>
           <t>WizAccountant Mobile</t>
         </is>
       </c>
-      <c r="C47" s="4" t="inlineStr">
+      <c r="C47" s="6" t="inlineStr">
         <is>
           <t>iOS / Android</t>
         </is>
       </c>
-      <c r="D47" s="4" t="inlineStr">
+      <c r="D47" s="6" t="inlineStr">
         <is>
           <t>Deep links</t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr">
+      <c r="E47" s="6" t="inlineStr">
         <is>
           <t>Open entity from notification</t>
         </is>
       </c>
-      <c r="F47" s="4" t="inlineStr">
+      <c r="F47" s="6" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="n">
+      <c r="A48" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B48" s="5" t="inlineStr">
+      <c r="B48" s="7" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
+      <c r="C48" s="7" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D48" s="5" t="inlineStr">
+      <c r="D48" s="7" t="inlineStr">
         <is>
           <t>Idempotency store</t>
         </is>
       </c>
-      <c r="E48" s="5" t="inlineStr">
+      <c r="E48" s="7" t="inlineStr">
         <is>
           <t>Local SQLite: idempotencyKey → result hash</t>
         </is>
       </c>
-      <c r="F48" s="5" t="inlineStr">
+      <c r="F48" s="7" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="n">
+      <c r="A49" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B49" s="5" t="inlineStr">
+      <c r="B49" s="7" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
+      <c r="C49" s="7" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D49" s="5" t="inlineStr">
+      <c r="D49" s="7" t="inlineStr">
         <is>
           <t>Write handlers</t>
         </is>
       </c>
-      <c r="E49" s="5" t="inlineStr">
+      <c r="E49" s="7" t="inlineStr">
         <is>
           <t>Allowlisted post operations</t>
         </is>
       </c>
-      <c r="F49" s="5" t="inlineStr">
+      <c r="F49" s="7" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="n">
+      <c r="A50" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B50" s="5" t="inlineStr">
+      <c r="B50" s="7" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
+      <c r="C50" s="7" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="D50" s="7" t="inlineStr">
         <is>
           <t>Transactions</t>
         </is>
       </c>
-      <c r="E50" s="5" t="inlineStr">
+      <c r="E50" s="7" t="inlineStr">
         <is>
           <t>BeginTran / Commit / Rollback per action</t>
         </is>
       </c>
-      <c r="F50" s="5" t="inlineStr">
+      <c r="F50" s="7" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="n">
+      <c r="A51" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B51" s="5" t="inlineStr">
+      <c r="B51" s="7" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
+      <c r="C51" s="7" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D51" s="5" t="inlineStr">
+      <c r="D51" s="7" t="inlineStr">
         <is>
           <t>StartNewBatch</t>
         </is>
       </c>
-      <c r="E51" s="5" t="inlineStr">
+      <c r="E51" s="7" t="inlineStr">
         <is>
           <t>Separate audit batches per post</t>
         </is>
       </c>
-      <c r="F51" s="5" t="inlineStr">
+      <c r="F51" s="7" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="n">
+      <c r="A52" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B52" s="5" t="inlineStr">
+      <c r="B52" s="7" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr">
+      <c r="C52" s="7" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="D52" s="7" t="inlineStr">
         <is>
           <t>Error mapping</t>
         </is>
       </c>
-      <c r="E52" s="5" t="inlineStr">
+      <c r="E52" s="7" t="inlineStr">
         <is>
           <t>Evolution exceptions → stable error codes</t>
         </is>
       </c>
-      <c r="F52" s="5" t="inlineStr">
+      <c r="F52" s="7" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="n">
+      <c r="A53" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B53" s="5" t="inlineStr">
+      <c r="B53" s="7" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr">
+      <c r="C53" s="7" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D53" s="5" t="inlineStr">
+      <c r="D53" s="7" t="inlineStr">
         <is>
           <t>Consent (optional)</t>
         </is>
       </c>
-      <c r="E53" s="5" t="inlineStr">
+      <c r="E53" s="7" t="inlineStr">
         <is>
           <t>Tray: Allow cloud to post for 1 hour</t>
         </is>
       </c>
-      <c r="F53" s="5" t="inlineStr">
+      <c r="F53" s="7" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="n">
+      <c r="A54" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B54" s="5" t="inlineStr">
+      <c r="B54" s="7" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr">
+      <c r="C54" s="7" t="inlineStr">
         <is>
           <t>Sage SDK</t>
         </is>
       </c>
-      <c r="D54" s="5" t="inlineStr">
+      <c r="D54" s="7" t="inlineStr">
         <is>
           <t>GL</t>
         </is>
       </c>
-      <c r="E54" s="5" t="inlineStr">
+      <c r="E54" s="7" t="inlineStr">
         <is>
           <t>GLTransaction.Post; journal batch create only — VAT legs per SDK</t>
         </is>
       </c>
-      <c r="F54" s="5" t="inlineStr">
+      <c r="F54" s="7" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="n">
+      <c r="A55" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B55" s="5" t="inlineStr">
+      <c r="B55" s="7" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C55" s="5" t="inlineStr">
+      <c r="C55" s="7" t="inlineStr">
         <is>
           <t>Sage SDK</t>
         </is>
       </c>
-      <c r="D55" s="5" t="inlineStr">
+      <c r="D55" s="7" t="inlineStr">
         <is>
           <t>AR</t>
         </is>
       </c>
-      <c r="E55" s="5" t="inlineStr">
+      <c r="E55" s="7" t="inlineStr">
         <is>
           <t>CustomerTransaction.Post; Allocations.Save — Codes per site config</t>
         </is>
       </c>
-      <c r="F55" s="5" t="inlineStr">
+      <c r="F55" s="7" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="n">
+      <c r="A56" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B56" s="5" t="inlineStr">
+      <c r="B56" s="7" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C56" s="5" t="inlineStr">
+      <c r="C56" s="7" t="inlineStr">
         <is>
           <t>Sage SDK</t>
         </is>
       </c>
-      <c r="D56" s="5" t="inlineStr">
+      <c r="D56" s="7" t="inlineStr">
         <is>
           <t>AP</t>
         </is>
       </c>
-      <c r="E56" s="5" t="inlineStr">
+      <c r="E56" s="7" t="inlineStr">
         <is>
           <t>SupplierTransaction.Post; Allocations.Save — Codes per site config</t>
         </is>
       </c>
-      <c r="F56" s="5" t="inlineStr">
+      <c r="F56" s="7" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="n">
+      <c r="A57" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B57" s="5" t="inlineStr">
+      <c r="B57" s="7" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C57" s="5" t="inlineStr">
+      <c r="C57" s="7" t="inlineStr">
         <is>
           <t>Sage SDK</t>
         </is>
       </c>
-      <c r="D57" s="5" t="inlineStr">
+      <c r="D57" s="7" t="inlineStr">
         <is>
           <t>Master (limited)</t>
         </is>
       </c>
-      <c r="E57" s="5" t="inlineStr">
+      <c r="E57" s="7" t="inlineStr">
         <is>
           <t>Customer.Save, Supplier.Save — Role-gated</t>
         </is>
       </c>
-      <c r="F57" s="5" t="inlineStr">
+      <c r="F57" s="7" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="n">
+      <c r="A58" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B58" s="5" t="inlineStr">
+      <c r="B58" s="7" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C58" s="5" t="inlineStr">
+      <c r="C58" s="7" t="inlineStr">
         <is>
           <t>Sage SDK</t>
         </is>
       </c>
-      <c r="D58" s="5" t="inlineStr">
+      <c r="D58" s="7" t="inlineStr">
         <is>
           <t>Orders (optional 3b)</t>
         </is>
       </c>
-      <c r="E58" s="5" t="inlineStr">
+      <c r="E58" s="7" t="inlineStr">
         <is>
           <t>SalesOrder/PurchaseOrder Save + Process partial — Sub-phase</t>
         </is>
       </c>
-      <c r="F58" s="5" t="inlineStr">
+      <c r="F58" s="7" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="n">
+      <c r="A59" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B59" s="5" t="inlineStr">
+      <c r="B59" s="7" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C59" s="5" t="inlineStr">
+      <c r="C59" s="7" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D59" s="5" t="inlineStr">
+      <c r="D59" s="7" t="inlineStr">
         <is>
           <t>Approval queue</t>
         </is>
       </c>
-      <c r="E59" s="5" t="inlineStr">
+      <c r="E59" s="7" t="inlineStr">
         <is>
           <t>Proposed journal/payment → approver → execute</t>
         </is>
       </c>
-      <c r="F59" s="5" t="inlineStr">
+      <c r="F59" s="7" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="n">
+      <c r="A60" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B60" s="5" t="inlineStr">
+      <c r="B60" s="7" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C60" s="5" t="inlineStr">
+      <c r="C60" s="7" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D60" s="5" t="inlineStr">
+      <c r="D60" s="7" t="inlineStr">
         <is>
           <t>Maker-checker</t>
         </is>
       </c>
-      <c r="E60" s="5" t="inlineStr">
+      <c r="E60" s="7" t="inlineStr">
         <is>
           <t>Prepare vs approve roles</t>
         </is>
       </c>
-      <c r="F60" s="5" t="inlineStr">
+      <c r="F60" s="7" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="n">
+      <c r="A61" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B61" s="5" t="inlineStr">
+      <c r="B61" s="7" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C61" s="5" t="inlineStr">
+      <c r="C61" s="7" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D61" s="5" t="inlineStr">
+      <c r="D61" s="7" t="inlineStr">
         <is>
           <t>AI propose, human approve</t>
         </is>
       </c>
-      <c r="E61" s="5" t="inlineStr">
+      <c r="E61" s="7" t="inlineStr">
         <is>
           <t>Draft only until approved</t>
         </is>
       </c>
-      <c r="F61" s="5" t="inlineStr">
+      <c r="F61" s="7" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="n">
+      <c r="A62" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B62" s="5" t="inlineStr">
+      <c r="B62" s="7" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C62" s="5" t="inlineStr">
+      <c r="C62" s="7" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D62" s="5" t="inlineStr">
+      <c r="D62" s="7" t="inlineStr">
         <is>
           <t>Write audit</t>
         </is>
       </c>
-      <c r="E62" s="5" t="inlineStr">
+      <c r="E62" s="7" t="inlineStr">
         <is>
           <t>Before/after, user, approver, Evolution ref</t>
         </is>
       </c>
-      <c r="F62" s="5" t="inlineStr">
+      <c r="F62" s="7" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="n">
+      <c r="A63" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B63" s="5" t="inlineStr">
+      <c r="B63" s="7" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C63" s="5" t="inlineStr">
+      <c r="C63" s="7" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D63" s="5" t="inlineStr">
+      <c r="D63" s="7" t="inlineStr">
         <is>
           <t>Workflows (starter)</t>
         </is>
       </c>
-      <c r="E63" s="5" t="inlineStr">
+      <c r="E63" s="7" t="inlineStr">
         <is>
           <t>Month-end checklist, payment run proposal</t>
         </is>
       </c>
-      <c r="F63" s="5" t="inlineStr">
+      <c r="F63" s="7" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="n">
+      <c r="A64" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B64" s="5" t="inlineStr">
+      <c r="B64" s="7" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C64" s="5" t="inlineStr">
+      <c r="C64" s="7" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D64" s="5" t="inlineStr">
+      <c r="D64" s="7" t="inlineStr">
         <is>
           <t>Site config sync</t>
         </is>
       </c>
-      <c r="E64" s="5" t="inlineStr">
+      <c r="E64" s="7" t="inlineStr">
         <is>
           <t>Transaction codes, tax, branch</t>
         </is>
       </c>
-      <c r="F64" s="5" t="inlineStr">
+      <c r="F64" s="7" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="n">
+      <c r="A65" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B65" s="5" t="inlineStr">
+      <c r="B65" s="7" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C65" s="5" t="inlineStr">
+      <c r="C65" s="7" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D65" s="5" t="inlineStr">
+      <c r="D65" s="7" t="inlineStr">
         <is>
           <t>Rollback messaging</t>
         </is>
       </c>
-      <c r="E65" s="5" t="inlineStr">
+      <c r="E65" s="7" t="inlineStr">
         <is>
           <t>Posts not auto-reversed in product</t>
         </is>
       </c>
-      <c r="F65" s="5" t="inlineStr">
+      <c r="F65" s="7" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="5" t="n">
+      <c r="A66" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B66" s="5" t="inlineStr">
+      <c r="B66" s="7" t="inlineStr">
         <is>
           <t>WizAccountant Mobile</t>
         </is>
       </c>
-      <c r="C66" s="5" t="inlineStr">
+      <c r="C66" s="7" t="inlineStr">
         <is>
           <t>iOS / Android</t>
         </is>
       </c>
-      <c r="D66" s="5" t="inlineStr">
+      <c r="D66" s="7" t="inlineStr">
         <is>
           <t>Approval inbox</t>
         </is>
       </c>
-      <c r="E66" s="5" t="inlineStr">
+      <c r="E66" s="7" t="inlineStr">
         <is>
           <t>Pending journals, payments, allocations</t>
         </is>
       </c>
-      <c r="F66" s="5" t="inlineStr">
+      <c r="F66" s="7" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="n">
+      <c r="A67" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B67" s="5" t="inlineStr">
+      <c r="B67" s="7" t="inlineStr">
         <is>
           <t>WizAccountant Mobile</t>
         </is>
       </c>
-      <c r="C67" s="5" t="inlineStr">
+      <c r="C67" s="7" t="inlineStr">
         <is>
           <t>iOS / Android</t>
         </is>
       </c>
-      <c r="D67" s="5" t="inlineStr">
+      <c r="D67" s="7" t="inlineStr">
         <is>
           <t>Approve / reject</t>
         </is>
       </c>
-      <c r="E67" s="5" t="inlineStr">
+      <c r="E67" s="7" t="inlineStr">
         <is>
           <t>Maker-checker with comment</t>
         </is>
       </c>
-      <c r="F67" s="5" t="inlineStr">
+      <c r="F67" s="7" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="5" t="n">
+      <c r="A68" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B68" s="5" t="inlineStr">
+      <c r="B68" s="7" t="inlineStr">
         <is>
           <t>WizAccountant Mobile</t>
         </is>
       </c>
-      <c r="C68" s="5" t="inlineStr">
+      <c r="C68" s="7" t="inlineStr">
         <is>
           <t>iOS / Android</t>
         </is>
       </c>
-      <c r="D68" s="5" t="inlineStr">
+      <c r="D68" s="7" t="inlineStr">
         <is>
           <t>Push notifications</t>
         </is>
       </c>
-      <c r="E68" s="5" t="inlineStr">
+      <c r="E68" s="7" t="inlineStr">
         <is>
           <t>Approval required + deep link</t>
         </is>
       </c>
-      <c r="F68" s="5" t="inlineStr">
+      <c r="F68" s="7" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="5" t="n">
+      <c r="A69" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B69" s="5" t="inlineStr">
+      <c r="B69" s="7" t="inlineStr">
         <is>
           <t>WizAccountant Mobile</t>
         </is>
       </c>
-      <c r="C69" s="5" t="inlineStr">
+      <c r="C69" s="7" t="inlineStr">
         <is>
           <t>iOS / Android</t>
         </is>
       </c>
-      <c r="D69" s="5" t="inlineStr">
+      <c r="D69" s="7" t="inlineStr">
         <is>
           <t>AI drafts</t>
         </is>
       </c>
-      <c r="E69" s="5" t="inlineStr">
+      <c r="E69" s="7" t="inlineStr">
         <is>
           <t>View proposal; approve via flow</t>
         </is>
       </c>
-      <c r="F69" s="5" t="inlineStr">
+      <c r="F69" s="7" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="5" t="n">
+      <c r="A70" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B70" s="5" t="inlineStr">
+      <c r="B70" s="7" t="inlineStr">
         <is>
           <t>WizAccountant Mobile</t>
         </is>
       </c>
-      <c r="C70" s="5" t="inlineStr">
+      <c r="C70" s="7" t="inlineStr">
         <is>
           <t>iOS / Android</t>
         </is>
       </c>
-      <c r="D70" s="5" t="inlineStr">
+      <c r="D70" s="7" t="inlineStr">
         <is>
           <t>Audit (read)</t>
         </is>
       </c>
-      <c r="E70" s="5" t="inlineStr">
+      <c r="E70" s="7" t="inlineStr">
         <is>
           <t>Approval history per item</t>
         </is>
       </c>
-      <c r="F70" s="5" t="inlineStr">
+      <c r="F70" s="7" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="6" t="n">
+      <c r="A71" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B71" s="6" t="inlineStr">
+      <c r="B71" s="8" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C71" s="6" t="inlineStr">
+      <c r="C71" s="8" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D71" s="6" t="inlineStr">
+      <c r="D71" s="8" t="inlineStr">
         <is>
           <t>Multi-company</t>
         </is>
       </c>
-      <c r="E71" s="6" t="inlineStr">
+      <c r="E71" s="8" t="inlineStr">
         <is>
           <t>One agent → multiple company DBs</t>
         </is>
       </c>
-      <c r="F71" s="6" t="inlineStr">
+      <c r="F71" s="8" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="6" t="n">
+      <c r="A72" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B72" s="6" t="inlineStr">
+      <c r="B72" s="8" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C72" s="6" t="inlineStr">
+      <c r="C72" s="8" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D72" s="6" t="inlineStr">
+      <c r="D72" s="8" t="inlineStr">
         <is>
           <t>Branch context</t>
         </is>
       </c>
-      <c r="E72" s="6" t="inlineStr">
+      <c r="E72" s="8" t="inlineStr">
         <is>
           <t>SetBranchContext per site</t>
         </is>
       </c>
-      <c r="F72" s="6" t="inlineStr">
+      <c r="F72" s="8" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="6" t="n">
+      <c r="A73" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B73" s="6" t="inlineStr">
+      <c r="B73" s="8" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C73" s="6" t="inlineStr">
+      <c r="C73" s="8" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D73" s="6" t="inlineStr">
+      <c r="D73" s="8" t="inlineStr">
         <is>
           <t>Heavy modules</t>
         </is>
       </c>
-      <c r="E73" s="6" t="inlineStr">
+      <c r="E73" s="8" t="inlineStr">
         <is>
           <t>CN, RTS, inventory adj, warehouse transfer</t>
         </is>
       </c>
-      <c r="F73" s="6" t="inlineStr">
+      <c r="F73" s="8" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="6" t="n">
+      <c r="A74" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B74" s="6" t="inlineStr">
+      <c r="B74" s="8" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C74" s="6" t="inlineStr">
+      <c r="C74" s="8" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D74" s="6" t="inlineStr">
+      <c r="D74" s="8" t="inlineStr">
         <is>
           <t>Order processing</t>
         </is>
       </c>
-      <c r="E74" s="6" t="inlineStr">
+      <c r="E74" s="8" t="inlineStr">
         <is>
           <t>SO/PO Process, partial, Complete</t>
         </is>
       </c>
-      <c r="F74" s="6" t="inlineStr">
+      <c r="F74" s="8" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="6" t="n">
+      <c r="A75" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B75" s="6" t="inlineStr">
+      <c r="B75" s="8" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C75" s="6" t="inlineStr">
+      <c r="C75" s="8" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D75" s="6" t="inlineStr">
+      <c r="D75" s="8" t="inlineStr">
         <is>
           <t>Offline queue (optional)</t>
         </is>
       </c>
-      <c r="E75" s="6" t="inlineStr">
+      <c r="E75" s="8" t="inlineStr">
         <is>
           <t>Buffer approved jobs when Sage busy</t>
         </is>
       </c>
-      <c r="F75" s="6" t="inlineStr">
+      <c r="F75" s="8" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="6" t="n">
+      <c r="A76" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B76" s="6" t="inlineStr">
+      <c r="B76" s="8" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C76" s="6" t="inlineStr">
+      <c r="C76" s="8" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D76" s="6" t="inlineStr">
+      <c r="D76" s="8" t="inlineStr">
         <is>
           <t>Practice mode</t>
         </is>
       </c>
-      <c r="E76" s="6" t="inlineStr">
+      <c r="E76" s="8" t="inlineStr">
         <is>
           <t>One firm, many client sites</t>
         </is>
       </c>
-      <c r="F76" s="6" t="inlineStr">
+      <c r="F76" s="8" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="6" t="n">
+      <c r="A77" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B77" s="6" t="inlineStr">
+      <c r="B77" s="8" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C77" s="6" t="inlineStr">
+      <c r="C77" s="8" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D77" s="6" t="inlineStr">
+      <c r="D77" s="8" t="inlineStr">
         <is>
           <t>RBAC</t>
         </is>
       </c>
-      <c r="E77" s="6" t="inlineStr">
+      <c r="E77" s="8" t="inlineStr">
         <is>
           <t>Read vs propose vs approve vs admin</t>
         </is>
       </c>
-      <c r="F77" s="6" t="inlineStr">
+      <c r="F77" s="8" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="6" t="n">
+      <c r="A78" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B78" s="6" t="inlineStr">
+      <c r="B78" s="8" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C78" s="6" t="inlineStr">
+      <c r="C78" s="8" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D78" s="6" t="inlineStr">
+      <c r="D78" s="8" t="inlineStr">
         <is>
           <t>SSO</t>
         </is>
       </c>
-      <c r="E78" s="6" t="inlineStr">
+      <c r="E78" s="8" t="inlineStr">
         <is>
           <t>Azure AD / Google</t>
         </is>
       </c>
-      <c r="F78" s="6" t="inlineStr">
+      <c r="F78" s="8" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="6" t="n">
+      <c r="A79" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B79" s="6" t="inlineStr">
+      <c r="B79" s="8" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C79" s="6" t="inlineStr">
+      <c r="C79" s="8" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D79" s="6" t="inlineStr">
+      <c r="D79" s="8" t="inlineStr">
         <is>
           <t>Monitoring</t>
         </is>
       </c>
-      <c r="E79" s="6" t="inlineStr">
+      <c r="E79" s="8" t="inlineStr">
         <is>
           <t>Site SLA, failed job alerts</t>
         </is>
       </c>
-      <c r="F79" s="6" t="inlineStr">
+      <c r="F79" s="8" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="6" t="n">
+      <c r="A80" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B80" s="6" t="inlineStr">
+      <c r="B80" s="8" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C80" s="6" t="inlineStr">
+      <c r="C80" s="8" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D80" s="6" t="inlineStr">
+      <c r="D80" s="8" t="inlineStr">
         <is>
           <t>Billing</t>
         </is>
       </c>
-      <c r="E80" s="6" t="inlineStr">
+      <c r="E80" s="8" t="inlineStr">
         <is>
           <t>Per site / per user hooks</t>
         </is>
       </c>
-      <c r="F80" s="6" t="inlineStr">
+      <c r="F80" s="8" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="6" t="n">
+      <c r="A81" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B81" s="6" t="inlineStr">
+      <c r="B81" s="8" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C81" s="6" t="inlineStr">
+      <c r="C81" s="8" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D81" s="6" t="inlineStr">
+      <c r="D81" s="8" t="inlineStr">
         <is>
           <t>Compliance</t>
         </is>
       </c>
-      <c r="E81" s="6" t="inlineStr">
+      <c r="E81" s="8" t="inlineStr">
         <is>
           <t>DPA templates, retention</t>
         </is>
       </c>
-      <c r="F81" s="6" t="inlineStr">
+      <c r="F81" s="8" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="6" t="n">
+      <c r="A82" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B82" s="6" t="inlineStr">
+      <c r="B82" s="8" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C82" s="6" t="inlineStr">
+      <c r="C82" s="8" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D82" s="6" t="inlineStr">
+      <c r="D82" s="8" t="inlineStr">
         <is>
           <t>Advanced AI</t>
         </is>
       </c>
-      <c r="E82" s="6" t="inlineStr">
+      <c r="E82" s="8" t="inlineStr">
         <is>
           <t>Multi-step workflows; doc upload draft</t>
         </is>
       </c>
-      <c r="F82" s="6" t="inlineStr">
+      <c r="F82" s="8" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="6" t="n">
+      <c r="A83" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B83" s="6" t="inlineStr">
+      <c r="B83" s="8" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C83" s="6" t="inlineStr">
+      <c r="C83" s="8" t="inlineStr">
         <is>
           <t>Sage SDK</t>
         </is>
       </c>
-      <c r="D83" s="6" t="inlineStr">
+      <c r="D83" s="8" t="inlineStr">
         <is>
           <t>Inventory</t>
         </is>
       </c>
-      <c r="E83" s="6" t="inlineStr">
+      <c r="E83" s="8" t="inlineStr">
         <is>
           <t>InventoryTransaction.Post; CN/RTS Process; warehouse</t>
         </is>
       </c>
-      <c r="F83" s="6" t="inlineStr">
+      <c r="F83" s="8" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="6" t="n">
+      <c r="A84" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B84" s="6" t="inlineStr">
+      <c r="B84" s="8" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C84" s="6" t="inlineStr">
+      <c r="C84" s="8" t="inlineStr">
         <is>
           <t>Sage SDK</t>
         </is>
       </c>
-      <c r="D84" s="6" t="inlineStr">
+      <c r="D84" s="8" t="inlineStr">
         <is>
           <t>Orders</t>
         </is>
       </c>
-      <c r="E84" s="6" t="inlineStr">
+      <c r="E84" s="8" t="inlineStr">
         <is>
           <t>Full SO/PO lifecycle</t>
         </is>
       </c>
-      <c r="F84" s="6" t="inlineStr">
+      <c r="F84" s="8" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="6" t="n">
+      <c r="A85" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B85" s="6" t="inlineStr">
+      <c r="B85" s="8" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C85" s="6" t="inlineStr">
+      <c r="C85" s="8" t="inlineStr">
         <is>
           <t>Sage SDK</t>
         </is>
       </c>
-      <c r="D85" s="6" t="inlineStr">
+      <c r="D85" s="8" t="inlineStr">
         <is>
           <t>CRM</t>
         </is>
       </c>
-      <c r="E85" s="6" t="inlineStr">
+      <c r="E85" s="8" t="inlineStr">
         <is>
           <t>Incidents (if needed)</t>
         </is>
       </c>
-      <c r="F85" s="6" t="inlineStr">
+      <c r="F85" s="8" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="6" t="n">
+      <c r="A86" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B86" s="6" t="inlineStr">
+      <c r="B86" s="8" t="inlineStr">
         <is>
           <t>WizConnector</t>
         </is>
       </c>
-      <c r="C86" s="6" t="inlineStr">
+      <c r="C86" s="8" t="inlineStr">
         <is>
           <t>Sage SDK</t>
         </is>
       </c>
-      <c r="D86" s="6" t="inlineStr">
+      <c r="D86" s="8" t="inlineStr">
         <is>
           <t>Job costing</t>
         </is>
       </c>
-      <c r="E86" s="6" t="inlineStr">
+      <c r="E86" s="8" t="inlineStr">
         <is>
           <t>Job card Save only (no process)</t>
         </is>
       </c>
-      <c r="F86" s="6" t="inlineStr">
+      <c r="F86" s="8" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="6" t="n">
+      <c r="A87" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B87" s="6" t="inlineStr">
+      <c r="B87" s="8" t="inlineStr">
         <is>
           <t>WizAccountant Mobile</t>
         </is>
       </c>
-      <c r="C87" s="6" t="inlineStr">
+      <c r="C87" s="8" t="inlineStr">
         <is>
           <t>iOS / Android</t>
         </is>
       </c>
-      <c r="D87" s="6" t="inlineStr">
+      <c r="D87" s="8" t="inlineStr">
         <is>
           <t>Practice mode</t>
         </is>
       </c>
-      <c r="E87" s="6" t="inlineStr">
+      <c r="E87" s="8" t="inlineStr">
         <is>
           <t>Switch client site for accounting firms</t>
         </is>
       </c>
-      <c r="F87" s="6" t="inlineStr">
+      <c r="F87" s="8" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="6" t="n">
+      <c r="A88" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B88" s="6" t="inlineStr">
+      <c r="B88" s="8" t="inlineStr">
         <is>
           <t>WizAccountant Mobile</t>
         </is>
       </c>
-      <c r="C88" s="6" t="inlineStr">
+      <c r="C88" s="8" t="inlineStr">
         <is>
           <t>iOS / Android</t>
         </is>
       </c>
-      <c r="D88" s="6" t="inlineStr">
+      <c r="D88" s="8" t="inlineStr">
         <is>
           <t>Inventory (read)</t>
         </is>
       </c>
-      <c r="E88" s="6" t="inlineStr">
+      <c r="E88" s="8" t="inlineStr">
         <is>
           <t>Stock lookup, low-stock push alert</t>
         </is>
       </c>
-      <c r="F88" s="6" t="inlineStr">
+      <c r="F88" s="8" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="6" t="n">
+      <c r="A89" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B89" s="6" t="inlineStr">
+      <c r="B89" s="8" t="inlineStr">
         <is>
           <t>WizAccountant Mobile</t>
         </is>
       </c>
-      <c r="C89" s="6" t="inlineStr">
+      <c r="C89" s="8" t="inlineStr">
         <is>
           <t>iOS / Android</t>
         </is>
       </c>
-      <c r="D89" s="6" t="inlineStr">
+      <c r="D89" s="8" t="inlineStr">
         <is>
           <t>Workflows</t>
         </is>
       </c>
-      <c r="E89" s="6" t="inlineStr">
+      <c r="E89" s="8" t="inlineStr">
         <is>
           <t>Starter checklist steps from phone</t>
         </is>
       </c>
-      <c r="F89" s="6" t="inlineStr">
+      <c r="F89" s="8" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="6" t="n">
+      <c r="A90" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B90" s="6" t="inlineStr">
+      <c r="B90" s="8" t="inlineStr">
         <is>
           <t>WizAccountant Mobile</t>
         </is>
       </c>
-      <c r="C90" s="6" t="inlineStr">
+      <c r="C90" s="8" t="inlineStr">
         <is>
           <t>iOS / Android</t>
         </is>
       </c>
-      <c r="D90" s="6" t="inlineStr">
+      <c r="D90" s="8" t="inlineStr">
         <is>
           <t>Tablet layout</t>
         </is>
       </c>
-      <c r="E90" s="6" t="inlineStr">
+      <c r="E90" s="8" t="inlineStr">
         <is>
           <t>iPad / Android tablet for approvers</t>
         </is>
       </c>
-      <c r="F90" s="6" t="inlineStr">
+      <c r="F90" s="8" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="6" t="n">
+      <c r="A91" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B91" s="6" t="inlineStr">
+      <c r="B91" s="8" t="inlineStr">
         <is>
           <t>WizAccountant Mobile</t>
         </is>
       </c>
-      <c r="C91" s="6" t="inlineStr">
+      <c r="C91" s="8" t="inlineStr">
         <is>
           <t>iOS / Android</t>
         </is>
       </c>
-      <c r="D91" s="6" t="inlineStr">
+      <c r="D91" s="8" t="inlineStr">
         <is>
           <t>App store release</t>
         </is>
       </c>
-      <c r="E91" s="6" t="inlineStr">
+      <c r="E91" s="8" t="inlineStr">
         <is>
           <t>Production signing, crash analytics, staged rollout</t>
         </is>
       </c>
-      <c r="F91" s="6" t="inlineStr">
+      <c r="F91" s="8" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="3" t="n">
+      <c r="A92" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B92" s="3" t="inlineStr">
+      <c r="B92" s="5" t="inlineStr">
         <is>
           <t>WizAccountant Cloud</t>
         </is>
       </c>
-      <c r="C92" s="3" t="inlineStr">
+      <c r="C92" s="5" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D92" s="3" t="inlineStr">
+      <c r="D92" s="5" t="inlineStr">
         <is>
           <t>API mobile-ready</t>
         </is>
       </c>
-      <c r="E92" s="3" t="inlineStr">
+      <c r="E92" s="5" t="inlineStr">
         <is>
           <t>JWT, same job endpoints — no native app in P1</t>
         </is>
       </c>
-      <c r="F92" s="3" t="inlineStr">
+      <c r="F92" s="5" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
@@ -5347,7 +6473,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5537,7 +6663,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5687,7 +6813,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5823,226 +6949,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Module</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Phases</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>GL</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1–3</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Accounts, journals</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>AR / AP</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1–3</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Masters, transactions, allocations</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Inventory</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2 read, 4 write</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Items, adjustments</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Sales / Purchase orders</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>3b / 4</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>High complexity</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>CRM / Job costing</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>4+</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Niche; job card no process via SDK</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="49" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>WizVPN / network tunnel to LAN</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Hosted customer DB restore as primary product</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Full cloud replacement of Evolution UI (Plan 3)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Raw SQL access from web or AI</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Evolution report printing via SDK</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Unrestricted SDK passthrough</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Cashbook / journal batch process via SDK</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Job card process/complete via SDK</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>